--- a/data/merged/2026-09-09/MERGED_IT_Spot-Cleaner_2026-09-09.xlsx
+++ b/data/merged/2026-09-09/MERGED_IT_Spot-Cleaner_2026-09-09.xlsx
@@ -6165,13 +6165,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>29</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>29</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6429,13 +6429,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>35</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>35</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6473,13 +6473,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>36</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>36</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -7040,94 +7040,6 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="49" name="Product 49">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId49" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="50" name="Product 50">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId50" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -7453,7 +7365,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BR51"/>
+  <dimension ref="A1:BR49"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -13970,129 +13882,127 @@
       <c r="B29" s="13"/>
       <c r="C29" s="14" t="inlineStr">
         <is>
-          <t>B0753NXDPR</t>
+          <t>B0BSHCQQ4W</t>
         </is>
       </c>
       <c r="D29" s="14"/>
       <c r="E29" s="14"/>
       <c r="F29" s="14" t="inlineStr">
         <is>
-          <t>Bissell</t>
+          <t>H.Koenig</t>
         </is>
       </c>
       <c r="G29" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/stores/BISSELL/page/EDA95B6C-7064-466B-BACA-347C73A9A423?lp_asin=B0753NXDPR&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.it/stores/HKoenig/page/978AEC1C-8AF0-4DD0-AECD-D6014C0418DD?lp_asin=B0BSHCQQ4W&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H29" s="14" t="inlineStr">
         <is>
-          <t>BISSELL Oxygen Boost Potenziatore Detergente 1 L 1134NsPer formule detergenti per pulitori portatili SpotClean, per moquett</t>
+          <t>H.Koenig Pulitore smacchiatore TWT77 per tessuti:Tappeti/Divani/Poltrone/Materassi, Serbatoi acqua pulita e sporca rimovibili</t>
         </is>
       </c>
       <c r="I29" s="14"/>
       <c r="J29" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0753NXDPR?psc=1</t>
+          <t>https://www.amazon.it/dp/B0BSHCQQ4W?psc=1</t>
         </is>
       </c>
       <c r="K29" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/31BhvLWbbNL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61W1ckv75YL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L29" s="14" t="inlineStr">
         <is>
-          <t>B0753NXDPR</t>
+          <t>B0BSHCQQ4W</t>
         </is>
       </c>
       <c r="M29" s="14" t="inlineStr">
         <is>
-          <t>Salute e cura della persona:Pulizia e cura della casa:Detergenti per la casa:Detergenti per tappeti:Detersivi lavaggio a macchina tappeti</t>
+          <t>Casa e cucina:Aspirapolvere e pulizia di pavimenti e finestre:Lavatappeti</t>
         </is>
       </c>
       <c r="N29" s="14" t="inlineStr">
         <is>
-          <t>Visualizza i Top 100 nella categoria Salute e</t>
+          <t>Visualizza i Top 100 nella categoria Casa e c</t>
         </is>
       </c>
       <c r="O29" s="15">
-        <v>1542</v>
+        <v>5093</v>
       </c>
       <c r="P29" s="15">
-        <v>-84</v>
+        <v>14633</v>
       </c>
       <c r="Q29" s="16">
-        <v>-0.06</v>
+        <v>0.75</v>
       </c>
       <c r="R29" s="17" t="inlineStr">
         <is>
-          <t>Detersivi lavaggio a macchina tappeti domestici</t>
+          <t>Lavatappeti</t>
         </is>
       </c>
       <c r="S29" s="18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16</t>
         </is>
       </c>
       <c r="T29" s="15">
-        <v>880</v>
+        <v>211</v>
       </c>
       <c r="U29" s="16">
-        <v>0.31</v>
+        <v>1.32</v>
       </c>
       <c r="V29" s="15">
-        <v>13191</v>
+        <v>12639</v>
       </c>
       <c r="W29" s="15" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>100</t>
         </is>
       </c>
       <c r="X29" s="15">
-        <v>2998</v>
+        <v>6704</v>
       </c>
       <c r="Y29" s="19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Z29" s="20">
-        <v>14.99</v>
+        <v>59.9</v>
       </c>
       <c r="AA29" s="4"/>
       <c r="AB29" s="1"/>
-      <c r="AC29" s="2">
-        <v>10</v>
-      </c>
+      <c r="AC29" s="2"/>
       <c r="AD29" s="19">
-        <v>9363</v>
+        <v>1086</v>
       </c>
       <c r="AE29" s="15">
-        <v>184</v>
+        <v>4</v>
       </c>
       <c r="AF29" s="21">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="AG29" s="22">
-        <v>0.2091</v>
+        <v>0.019</v>
       </c>
       <c r="AH29" s="20">
-        <v>5.19</v>
+        <v>9.79</v>
       </c>
       <c r="AI29" s="16">
-        <v>0.5</v>
+        <v>0.69</v>
       </c>
       <c r="AJ29"/>
       <c r="AK29" s="13" t="inlineStr">
         <is>
-          <t>2017-10-06</t>
+          <t>2023-02-26</t>
         </is>
       </c>
       <c r="AL29" s="19">
-        <v>3259</v>
+        <v>1291</v>
       </c>
       <c r="AM29" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AN29" s="13"/>
@@ -14102,21 +14012,33 @@
         <v>10</v>
       </c>
       <c r="AR29" s="19">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AS29" s="14" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>HomeHome by A</t>
         </is>
       </c>
       <c r="AT29" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
-        </is>
-      </c>
-      <c r="AU29" s="13"/>
-      <c r="AV29" s="14"/>
-      <c r="AW29" s="13"/>
+          <t>FBA</t>
+        </is>
+      </c>
+      <c r="AU29" s="13" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="AV29" s="14" t="inlineStr">
+        <is>
+          <t>Paris 75001 FR</t>
+        </is>
+      </c>
+      <c r="AW29" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2J1ZXSJG29176</t>
+        </is>
+      </c>
       <c r="AX29" s="13"/>
       <c r="AY29" s="13" t="inlineStr">
         <is>
@@ -14147,47 +14069,47 @@
       </c>
       <c r="BJ29" s="23" t="inlineStr">
         <is>
-          <t>1,1 kg</t>
+          <t>4 kg</t>
         </is>
       </c>
       <c r="BK29" s="23" t="inlineStr">
         <is>
-          <t>1.10 kg</t>
+          <t>4.00 kg</t>
         </is>
       </c>
       <c r="BL29" s="23" t="inlineStr">
         <is>
-          <t>7 x 12 x 23,8 cm</t>
+          <t>36.5 x 24.5 x 31.8 cm</t>
         </is>
       </c>
       <c r="BM29" s="23" t="inlineStr">
         <is>
-          <t>7.00 x 12.00 x 23.80 cm</t>
+          <t>36.50 x 24.50 x 31.80 cm</t>
         </is>
       </c>
       <c r="BN29" s="23" t="inlineStr">
         <is>
-          <t>1.1 kg</t>
+          <t>5.88 kg</t>
         </is>
       </c>
       <c r="BO29" s="23" t="inlineStr">
         <is>
-          <t>1.10 kg</t>
+          <t>5.88 kg</t>
         </is>
       </c>
       <c r="BP29" s="23" t="inlineStr">
         <is>
-          <t>23.5 x 11.9 x 6.9 cm</t>
+          <t>45 x 38 x 29 cm</t>
         </is>
       </c>
       <c r="BQ29" s="23" t="inlineStr">
         <is>
-          <t>23.50 x 11.90 x 6.90 cm</t>
+          <t>45.00 x 38.00 x 29.00 cm</t>
         </is>
       </c>
       <c r="BR29" s="13" t="inlineStr">
         <is>
-          <t>小包裹</t>
+          <t>轻型标准大件</t>
         </is>
       </c>
     </row>
@@ -14198,40 +14120,40 @@
       <c r="B30" s="13"/>
       <c r="C30" s="14" t="inlineStr">
         <is>
-          <t>B0BSHCQQ4W</t>
+          <t>B0D2HFLM1C</t>
         </is>
       </c>
       <c r="D30" s="14"/>
       <c r="E30" s="14"/>
       <c r="F30" s="14" t="inlineStr">
         <is>
-          <t>H.Koenig</t>
+          <t>HAUSHOF</t>
         </is>
       </c>
       <c r="G30" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/stores/HKoenig/page/978AEC1C-8AF0-4DD0-AECD-D6014C0418DD?lp_asin=B0BSHCQQ4W&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.it/stores/HAUSHOF/page/9EE9CFD0-E18C-46CA-98BB-FA1050DF3283?lp_asin=B0D2HFLM1C&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H30" s="14" t="inlineStr">
         <is>
-          <t>H.Koenig Pulitore smacchiatore TWT77 per tessuti:Tappeti/Divani/Poltrone/Materassi, Serbatoi acqua pulita e sporca rimovibili</t>
+          <t>HAUSHOF StainZapper Pro - Lavatappeti Portatile 450W 11,5kPas1,5L lava tappezzeria ad Acqua con Detergente e Spazzola per G</t>
         </is>
       </c>
       <c r="I30" s="14"/>
       <c r="J30" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0BSHCQQ4W?psc=1</t>
+          <t>https://www.amazon.it/dp/B0D2HFLM1C?psc=1</t>
         </is>
       </c>
       <c r="K30" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61W1ckv75YL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T4/images/I/414TgmW8eiL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L30" s="14" t="inlineStr">
         <is>
-          <t>B0BSHCQQ4W</t>
+          <t>B0D2HFLM1C</t>
         </is>
       </c>
       <c r="M30" s="14" t="inlineStr">
@@ -14245,13 +14167,13 @@
         </is>
       </c>
       <c r="O30" s="15">
-        <v>5093</v>
+        <v>11254</v>
       </c>
       <c r="P30" s="15">
-        <v>14633</v>
+        <v>-3242</v>
       </c>
       <c r="Q30" s="16">
-        <v>0.75</v>
+        <v>-0.4</v>
       </c>
       <c r="R30" s="17" t="inlineStr">
         <is>
@@ -14260,65 +14182,65 @@
       </c>
       <c r="S30" s="18" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>26</t>
         </is>
       </c>
       <c r="T30" s="15">
-        <v>211</v>
+        <v>139</v>
       </c>
       <c r="U30" s="16">
-        <v>1.32</v>
+        <v>7.85</v>
       </c>
       <c r="V30" s="15">
-        <v>12639</v>
+        <v>12509</v>
       </c>
       <c r="W30" s="15" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>50</t>
         </is>
       </c>
       <c r="X30" s="15">
-        <v>6704</v>
+        <v>4384</v>
       </c>
       <c r="Y30" s="19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z30" s="20">
-        <v>59.9</v>
+        <v>89.99</v>
       </c>
       <c r="AA30" s="4"/>
       <c r="AB30" s="1"/>
       <c r="AC30" s="2"/>
       <c r="AD30" s="19">
-        <v>1086</v>
+        <v>743</v>
       </c>
       <c r="AE30" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF30" s="21">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AG30" s="22">
-        <v>0.019</v>
+        <v>0.036000000000000004</v>
       </c>
       <c r="AH30" s="20">
-        <v>9.79</v>
+        <v>5.18</v>
       </c>
       <c r="AI30" s="16">
-        <v>0.69</v>
+        <v>0.79</v>
       </c>
       <c r="AJ30"/>
       <c r="AK30" s="13" t="inlineStr">
         <is>
-          <t>2023-02-26</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AL30" s="19">
-        <v>1291</v>
+        <v>775</v>
       </c>
       <c r="AM30" s="13" t="inlineStr">
         <is>
-          <t>FBA</t>
+          <t>AMZ</t>
         </is>
       </c>
       <c r="AN30" s="13"/>
@@ -14328,33 +14250,21 @@
         <v>10</v>
       </c>
       <c r="AR30" s="19">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AS30" s="14" t="inlineStr">
         <is>
-          <t>HomeHome by A</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="AT30" s="13" t="inlineStr">
         <is>
-          <t>FBA</t>
-        </is>
-      </c>
-      <c r="AU30" s="13" t="inlineStr">
-        <is>
-          <t>FR</t>
-        </is>
-      </c>
-      <c r="AV30" s="14" t="inlineStr">
-        <is>
-          <t>Paris 75001 FR</t>
-        </is>
-      </c>
-      <c r="AW30" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2J1ZXSJG29176</t>
-        </is>
-      </c>
+          <t>AMZ</t>
+        </is>
+      </c>
+      <c r="AU30" s="13"/>
+      <c r="AV30" s="14"/>
+      <c r="AW30" s="13"/>
       <c r="AX30" s="13"/>
       <c r="AY30" s="13" t="inlineStr">
         <is>
@@ -14385,47 +14295,43 @@
       </c>
       <c r="BJ30" s="23" t="inlineStr">
         <is>
-          <t>4 kg</t>
+          <t>3,85 Kilograms</t>
         </is>
       </c>
       <c r="BK30" s="23" t="inlineStr">
         <is>
-          <t>4.00 kg</t>
+          <t>3.85 kg</t>
         </is>
       </c>
       <c r="BL30" s="23" t="inlineStr">
         <is>
-          <t>36.5 x 24.5 x 31.8 cm</t>
-        </is>
-      </c>
-      <c r="BM30" s="23" t="inlineStr">
-        <is>
-          <t>36.50 x 24.50 x 31.80 cm</t>
-        </is>
-      </c>
+          <t>19,6P x 38,5l x 30H cm</t>
+        </is>
+      </c>
+      <c r="BM30" s="23"/>
       <c r="BN30" s="23" t="inlineStr">
         <is>
-          <t>5.88 kg</t>
+          <t>5.68 kg</t>
         </is>
       </c>
       <c r="BO30" s="23" t="inlineStr">
         <is>
-          <t>5.88 kg</t>
+          <t>5.68 kg</t>
         </is>
       </c>
       <c r="BP30" s="23" t="inlineStr">
         <is>
-          <t>45 x 38 x 29 cm</t>
+          <t>44.4 x 33.9 x 20 cm</t>
         </is>
       </c>
       <c r="BQ30" s="23" t="inlineStr">
         <is>
-          <t>45.00 x 38.00 x 29.00 cm</t>
+          <t>44.40 x 33.90 x 20.00 cm</t>
         </is>
       </c>
       <c r="BR30" s="13" t="inlineStr">
         <is>
-          <t>轻型标准大件</t>
+          <t>标准包裹</t>
         </is>
       </c>
     </row>
@@ -14436,40 +14342,40 @@
       <c r="B31" s="13"/>
       <c r="C31" s="14" t="inlineStr">
         <is>
-          <t>B0D2HFLM1C</t>
+          <t>B0GH6TBJVW</t>
         </is>
       </c>
       <c r="D31" s="14"/>
       <c r="E31" s="14"/>
       <c r="F31" s="14" t="inlineStr">
         <is>
-          <t>HAUSHOF</t>
+          <t>Kitcanis</t>
         </is>
       </c>
       <c r="G31" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/stores/HAUSHOF/page/9EE9CFD0-E18C-46CA-98BB-FA1050DF3283?lp_asin=B0D2HFLM1C&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Kitcanis</t>
         </is>
       </c>
       <c r="H31" s="14" t="inlineStr">
         <is>
-          <t>HAUSHOF StainZapper Pro - Lavatappeti Portatile 450W 11,5kPas1,5L lava tappezzeria ad Acqua con Detergente e Spazzola per G</t>
+          <t>Kitcanis Lavatappeti e Divani Lava e Asciuga 17KPa 600W, Pulitore Tessuti Compatto con 4 Accessori, Serbatoi Rimovibili 1.1L/</t>
         </is>
       </c>
       <c r="I31" s="14"/>
       <c r="J31" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0D2HFLM1C?psc=1</t>
+          <t>https://www.amazon.it/dp/B0GH6TBJVW?psc=1</t>
         </is>
       </c>
       <c r="K31" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T4/images/I/414TgmW8eiL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/51LdyRohTNL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L31" s="14" t="inlineStr">
         <is>
-          <t>B0D2HFLM1C</t>
+          <t>B0GH6TBJVW</t>
         </is>
       </c>
       <c r="M31" s="14" t="inlineStr">
@@ -14483,13 +14389,13 @@
         </is>
       </c>
       <c r="O31" s="15">
-        <v>11254</v>
+        <v>6557</v>
       </c>
       <c r="P31" s="15">
-        <v>-3242</v>
+        <v>5770</v>
       </c>
       <c r="Q31" s="16">
-        <v>-0.4</v>
+        <v>0.47</v>
       </c>
       <c r="R31" s="17" t="inlineStr">
         <is>
@@ -14498,17 +14404,17 @@
       </c>
       <c r="S31" s="18" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>37</t>
         </is>
       </c>
       <c r="T31" s="15">
-        <v>139</v>
+        <v>108</v>
       </c>
       <c r="U31" s="16">
-        <v>7.85</v>
+        <v>1.36</v>
       </c>
       <c r="V31" s="15">
-        <v>12509</v>
+        <v>12393</v>
       </c>
       <c r="W31" s="15" t="inlineStr">
         <is>
@@ -14516,47 +14422,47 @@
         </is>
       </c>
       <c r="X31" s="15">
-        <v>4384</v>
+        <v>5143</v>
       </c>
       <c r="Y31" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z31" s="20">
-        <v>89.99</v>
+        <v>114.75</v>
       </c>
       <c r="AA31" s="4"/>
       <c r="AB31" s="1"/>
       <c r="AC31" s="2"/>
       <c r="AD31" s="19">
-        <v>743</v>
+        <v>87</v>
       </c>
       <c r="AE31" s="15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AF31" s="21">
         <v>4.3</v>
       </c>
       <c r="AG31" s="22">
-        <v>0.036000000000000004</v>
+        <v>0.037000000000000005</v>
       </c>
       <c r="AH31" s="20">
-        <v>5.18</v>
+        <v>5.49</v>
       </c>
       <c r="AI31" s="16">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="AJ31"/>
       <c r="AK31" s="13" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="AL31" s="19">
-        <v>775</v>
+        <v>151</v>
       </c>
       <c r="AM31" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AN31" s="13"/>
@@ -14570,23 +14476,31 @@
       </c>
       <c r="AS31" s="14" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>BingBon</t>
         </is>
       </c>
       <c r="AT31" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
-        </is>
-      </c>
-      <c r="AU31" s="13"/>
-      <c r="AV31" s="14"/>
-      <c r="AW31" s="13"/>
+          <t>FBA</t>
+        </is>
+      </c>
+      <c r="AU31" s="13" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="AV31" s="14" t="inlineStr">
+        <is>
+          <t>青岛市 李沧区 山东省 266041 CN</t>
+        </is>
+      </c>
+      <c r="AW31" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3SC5MLKO5B7LX</t>
+        </is>
+      </c>
       <c r="AX31" s="13"/>
-      <c r="AY31" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="AY31" s="13"/>
       <c r="AZ31" s="13"/>
       <c r="BA31" s="13"/>
       <c r="BB31" s="13"/>
@@ -14604,45 +14518,45 @@
       <c r="BF31" s="13"/>
       <c r="BG31" s="13"/>
       <c r="BH31" s="14"/>
-      <c r="BI31" s="23" t="inlineStr">
-        <is>
-          <t>Scelta Amazon</t>
-        </is>
-      </c>
+      <c r="BI31" s="23"/>
       <c r="BJ31" s="23" t="inlineStr">
         <is>
-          <t>3,85 Kilograms</t>
+          <t>4,7 Kilograms</t>
         </is>
       </c>
       <c r="BK31" s="23" t="inlineStr">
         <is>
-          <t>3.85 kg</t>
+          <t>4.70 kg</t>
         </is>
       </c>
       <c r="BL31" s="23" t="inlineStr">
         <is>
-          <t>19,6P x 38,5l x 30H cm</t>
-        </is>
-      </c>
-      <c r="BM31" s="23"/>
+          <t>23 x 43 x 32 cm</t>
+        </is>
+      </c>
+      <c r="BM31" s="23" t="inlineStr">
+        <is>
+          <t>23.00 x 43.00 x 32.00 cm</t>
+        </is>
+      </c>
       <c r="BN31" s="23" t="inlineStr">
         <is>
-          <t>5.68 kg</t>
+          <t>4.7 kg</t>
         </is>
       </c>
       <c r="BO31" s="23" t="inlineStr">
         <is>
-          <t>5.68 kg</t>
+          <t>4.70 kg</t>
         </is>
       </c>
       <c r="BP31" s="23" t="inlineStr">
         <is>
-          <t>44.4 x 33.9 x 20 cm</t>
+          <t>43.6 x 32.6 x 23.4 cm</t>
         </is>
       </c>
       <c r="BQ31" s="23" t="inlineStr">
         <is>
-          <t>44.40 x 33.90 x 20.00 cm</t>
+          <t>43.60 x 32.60 x 23.40 cm</t>
         </is>
       </c>
       <c r="BR31" s="13" t="inlineStr">
@@ -14658,40 +14572,40 @@
       <c r="B32" s="13"/>
       <c r="C32" s="14" t="inlineStr">
         <is>
-          <t>B0GH6TBJVW</t>
+          <t>B0FHB8RB8F</t>
         </is>
       </c>
       <c r="D32" s="14"/>
       <c r="E32" s="14"/>
       <c r="F32" s="14" t="inlineStr">
         <is>
-          <t>Kitcanis</t>
+          <t>Cecotec</t>
         </is>
       </c>
       <c r="G32" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Kitcanis</t>
+          <t>https://www.amazon.it/Cecotec/b/ref=bl_dp_s_web_19986335031?ie=UTF8&amp;node=19986335031&amp;field-lbr_brands_browse-bin=Cecotec</t>
         </is>
       </c>
       <c r="H32" s="14" t="inlineStr">
         <is>
-          <t>Kitcanis Lavatappeti e Divani Lava e Asciuga 17KPa 600W, Pulitore Tessuti Compatto con 4 Accessori, Serbatoi Rimovibili 1.1L/</t>
+          <t>Cecotec Lavatappeti Aspirapolvere con Cavo Conga 7000 Carpet&amp;Spot Clean Steam. Max. 1700 W, Vapore, Serbatoio Acqua Pulita 16</t>
         </is>
       </c>
       <c r="I32" s="14"/>
       <c r="J32" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0GH6TBJVW?psc=1</t>
+          <t>https://www.amazon.it/dp/B0FHB8RB8F?psc=1</t>
         </is>
       </c>
       <c r="K32" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/51LdyRohTNL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/411-YObj2pL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L32" s="14" t="inlineStr">
         <is>
-          <t>B0GH6TBJVW</t>
+          <t>B0FHB8RB8F</t>
         </is>
       </c>
       <c r="M32" s="14" t="inlineStr">
@@ -14705,13 +14619,13 @@
         </is>
       </c>
       <c r="O32" s="15">
-        <v>6557</v>
+        <v>39727</v>
       </c>
       <c r="P32" s="15">
-        <v>5770</v>
+        <v>-28487</v>
       </c>
       <c r="Q32" s="16">
-        <v>0.47</v>
+        <v>-2.06</v>
       </c>
       <c r="R32" s="17" t="inlineStr">
         <is>
@@ -14720,65 +14634,59 @@
       </c>
       <c r="S32" s="18" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>52</t>
         </is>
       </c>
       <c r="T32" s="15">
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="U32" s="16">
-        <v>1.36</v>
+        <v>4.56</v>
       </c>
       <c r="V32" s="15">
-        <v>12393</v>
-      </c>
-      <c r="W32" s="15" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="X32" s="15">
-        <v>5143</v>
-      </c>
+        <v>11168</v>
+      </c>
+      <c r="W32" s="15"/>
+      <c r="X32" s="15"/>
       <c r="Y32" s="19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z32" s="20">
-        <v>114.75</v>
+        <v>148.9</v>
       </c>
       <c r="AA32" s="4"/>
       <c r="AB32" s="1"/>
       <c r="AC32" s="2"/>
       <c r="AD32" s="19">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="AE32" s="15">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="AF32" s="21">
         <v>4.3</v>
       </c>
       <c r="AG32" s="22">
-        <v>0.037000000000000005</v>
+        <v>0.1467</v>
       </c>
       <c r="AH32" s="20">
-        <v>5.49</v>
+        <v>9.35</v>
       </c>
       <c r="AI32" s="16">
-        <v>0.8</v>
+        <v>0.79</v>
       </c>
       <c r="AJ32"/>
       <c r="AK32" s="13" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="AL32" s="19">
-        <v>151</v>
+        <v>405</v>
       </c>
       <c r="AM32" s="13" t="inlineStr">
         <is>
-          <t>FBA</t>
+          <t>AMZ</t>
         </is>
       </c>
       <c r="AN32" s="13"/>
@@ -14788,35 +14696,27 @@
         <v>10</v>
       </c>
       <c r="AR32" s="19">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AS32" s="14" t="inlineStr">
         <is>
-          <t>BingBon</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="AT32" s="13" t="inlineStr">
         <is>
-          <t>FBA</t>
-        </is>
-      </c>
-      <c r="AU32" s="13" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="AV32" s="14" t="inlineStr">
-        <is>
-          <t>青岛市 李沧区 山东省 266041 CN</t>
-        </is>
-      </c>
-      <c r="AW32" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3SC5MLKO5B7LX</t>
-        </is>
-      </c>
+          <t>AMZ</t>
+        </is>
+      </c>
+      <c r="AU32" s="13"/>
+      <c r="AV32" s="14"/>
+      <c r="AW32" s="13"/>
       <c r="AX32" s="13"/>
-      <c r="AY32" s="13"/>
+      <c r="AY32" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="AZ32" s="13"/>
       <c r="BA32" s="13"/>
       <c r="BB32" s="13"/>
@@ -14834,50 +14734,46 @@
       <c r="BF32" s="13"/>
       <c r="BG32" s="13"/>
       <c r="BH32" s="14"/>
-      <c r="BI32" s="23"/>
+      <c r="BI32" s="23" t="inlineStr">
+        <is>
+          <t>Scelta Amazon</t>
+        </is>
+      </c>
       <c r="BJ32" s="23" t="inlineStr">
         <is>
-          <t>4,7 Kilograms</t>
-        </is>
-      </c>
-      <c r="BK32" s="23" t="inlineStr">
-        <is>
-          <t>4.70 kg</t>
-        </is>
-      </c>
+          <t>4,34 Chilogrammi</t>
+        </is>
+      </c>
+      <c r="BK32" s="23"/>
       <c r="BL32" s="23" t="inlineStr">
         <is>
-          <t>23 x 43 x 32 cm</t>
-        </is>
-      </c>
-      <c r="BM32" s="23" t="inlineStr">
-        <is>
-          <t>23.00 x 43.00 x 32.00 cm</t>
-        </is>
-      </c>
+          <t>24P x 32l x 30H cm</t>
+        </is>
+      </c>
+      <c r="BM32" s="23"/>
       <c r="BN32" s="23" t="inlineStr">
         <is>
-          <t>4.7 kg</t>
+          <t>5.91 kg</t>
         </is>
       </c>
       <c r="BO32" s="23" t="inlineStr">
         <is>
-          <t>4.70 kg</t>
+          <t>5.91 kg</t>
         </is>
       </c>
       <c r="BP32" s="23" t="inlineStr">
         <is>
-          <t>43.6 x 32.6 x 23.4 cm</t>
+          <t>41.3 x 36.4 x 28.8 cm</t>
         </is>
       </c>
       <c r="BQ32" s="23" t="inlineStr">
         <is>
-          <t>43.60 x 32.60 x 23.40 cm</t>
+          <t>41.30 x 36.40 x 28.80 cm</t>
         </is>
       </c>
       <c r="BR32" s="13" t="inlineStr">
         <is>
-          <t>标准包裹</t>
+          <t>轻型标准大件</t>
         </is>
       </c>
     </row>
@@ -14888,40 +14784,40 @@
       <c r="B33" s="13"/>
       <c r="C33" s="14" t="inlineStr">
         <is>
-          <t>B0FHB8RB8F</t>
+          <t>B0DFLYY2H7</t>
         </is>
       </c>
       <c r="D33" s="14"/>
       <c r="E33" s="14"/>
       <c r="F33" s="14" t="inlineStr">
         <is>
-          <t>Cecotec</t>
+          <t>Vacmaster</t>
         </is>
       </c>
       <c r="G33" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/Cecotec/b/ref=bl_dp_s_web_19986335031?ie=UTF8&amp;node=19986335031&amp;field-lbr_brands_browse-bin=Cecotec</t>
+          <t>https://www.amazon.it/stores/VACMASTER/page/F372FF16-5498-423D-9923-A4EFB43DC86B?lp_asin=B0DFLYY2H7&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H33" s="14" t="inlineStr">
         <is>
-          <t>Cecotec Lavatappeti Aspirapolvere con Cavo Conga 7000 Carpet&amp;Spot Clean Steam. Max. 1700 W, Vapore, Serbatoio Acqua Pulita 16</t>
+          <t>Vacmaster Lavatappeti lava tappezzeria, Ideale per Pulisci Scale, divano, Sedili Auto, Moquette e Tappeti, lava divani e aspi</t>
         </is>
       </c>
       <c r="I33" s="14"/>
       <c r="J33" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0FHB8RB8F?psc=1</t>
+          <t>https://www.amazon.it/dp/B0DFLYY2H7?psc=1</t>
         </is>
       </c>
       <c r="K33" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/411-YObj2pL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41n21y5gWdL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L33" s="14" t="inlineStr">
         <is>
-          <t>B0FHB8RB8F</t>
+          <t>B0DFLYY2H7</t>
         </is>
       </c>
       <c r="M33" s="14" t="inlineStr">
@@ -14935,13 +14831,13 @@
         </is>
       </c>
       <c r="O33" s="15">
-        <v>39727</v>
+        <v>12058</v>
       </c>
       <c r="P33" s="15">
-        <v>-28487</v>
+        <v>22830</v>
       </c>
       <c r="Q33" s="16">
-        <v>-2.06</v>
+        <v>0.6</v>
       </c>
       <c r="R33" s="17" t="inlineStr">
         <is>
@@ -14950,17 +14846,17 @@
       </c>
       <c r="S33" s="18" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>29</t>
         </is>
       </c>
       <c r="T33" s="15">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="U33" s="16">
-        <v>4.56</v>
+        <v>-0.24</v>
       </c>
       <c r="V33" s="15">
-        <v>11168</v>
+        <v>9244</v>
       </c>
       <c r="W33" s="15"/>
       <c r="X33" s="15"/>
@@ -14968,25 +14864,25 @@
         <v>2</v>
       </c>
       <c r="Z33" s="20">
-        <v>148.9</v>
+        <v>122.21</v>
       </c>
       <c r="AA33" s="4"/>
       <c r="AB33" s="1"/>
       <c r="AC33" s="2"/>
       <c r="AD33" s="19">
-        <v>83</v>
+        <v>264</v>
       </c>
       <c r="AE33" s="15">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="AF33" s="21">
         <v>4.3</v>
       </c>
       <c r="AG33" s="22">
-        <v>0.1467</v>
+        <v>0.4032</v>
       </c>
       <c r="AH33" s="20">
-        <v>9.35</v>
+        <v>11.13</v>
       </c>
       <c r="AI33" s="16">
         <v>0.79</v>
@@ -14994,11 +14890,11 @@
       <c r="AJ33"/>
       <c r="AK33" s="13" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="AL33" s="19">
-        <v>405</v>
+        <v>734</v>
       </c>
       <c r="AM33" s="13" t="inlineStr">
         <is>
@@ -15012,7 +14908,7 @@
         <v>10</v>
       </c>
       <c r="AR33" s="19">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AS33" s="14" t="inlineStr">
         <is>
@@ -15026,7 +14922,11 @@
       </c>
       <c r="AU33" s="13"/>
       <c r="AV33" s="14"/>
-      <c r="AW33" s="13"/>
+      <c r="AW33" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AUAKXO7WRPF4V</t>
+        </is>
+      </c>
       <c r="AX33" s="13"/>
       <c r="AY33" s="13" t="inlineStr">
         <is>
@@ -15057,34 +14957,34 @@
       </c>
       <c r="BJ33" s="23" t="inlineStr">
         <is>
-          <t>4,34 Chilogrammi</t>
+          <t>11 Chilogrammi</t>
         </is>
       </c>
       <c r="BK33" s="23"/>
       <c r="BL33" s="23" t="inlineStr">
         <is>
-          <t>24P x 32l x 30H cm</t>
+          <t>39,4P x 35,5l x 57H cm</t>
         </is>
       </c>
       <c r="BM33" s="23"/>
       <c r="BN33" s="23" t="inlineStr">
         <is>
-          <t>5.91 kg</t>
+          <t>10.54 kg</t>
         </is>
       </c>
       <c r="BO33" s="23" t="inlineStr">
         <is>
-          <t>5.91 kg</t>
+          <t>10.54 kg</t>
         </is>
       </c>
       <c r="BP33" s="23" t="inlineStr">
         <is>
-          <t>41.3 x 36.4 x 28.8 cm</t>
+          <t>61 x 39.2 x 34 cm</t>
         </is>
       </c>
       <c r="BQ33" s="23" t="inlineStr">
         <is>
-          <t>41.30 x 36.40 x 28.80 cm</t>
+          <t>61.00 x 39.20 x 34.00 cm</t>
         </is>
       </c>
       <c r="BR33" s="13" t="inlineStr">
@@ -15100,40 +15000,40 @@
       <c r="B34" s="13"/>
       <c r="C34" s="14" t="inlineStr">
         <is>
-          <t>B0DFLYY2H7</t>
+          <t>B0FJFDG5PY</t>
         </is>
       </c>
       <c r="D34" s="14"/>
       <c r="E34" s="14"/>
       <c r="F34" s="14" t="inlineStr">
         <is>
-          <t>Vacmaster</t>
+          <t>Akitas</t>
         </is>
       </c>
       <c r="G34" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/stores/VACMASTER/page/F372FF16-5498-423D-9923-A4EFB43DC86B?lp_asin=B0DFLYY2H7&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.it/stores/Akitas/page/EE82F545-EF96-443C-8B75-30C504BE3C43?lp_asin=B0FJFDG5PY&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H34" s="14" t="inlineStr">
         <is>
-          <t>Vacmaster Lavatappeti lava tappezzeria, Ideale per Pulisci Scale, divano, Sedili Auto, Moquette e Tappeti, lava divani e aspi</t>
+          <t>Akitas X7 600W Lavatappeti e Divani Lava e Asciuga, 14kPa Potente Aspirazione, Lava Tappezzeria per Auto, Moquette, Materassi</t>
         </is>
       </c>
       <c r="I34" s="14"/>
       <c r="J34" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0DFLYY2H7?psc=1</t>
+          <t>https://www.amazon.it/dp/B0FJFDG5PY?psc=1</t>
         </is>
       </c>
       <c r="K34" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41n21y5gWdL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41eJu8zeBKL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L34" s="14" t="inlineStr">
         <is>
-          <t>B0DFLYY2H7</t>
+          <t>B0FJFDG5PY</t>
         </is>
       </c>
       <c r="M34" s="14" t="inlineStr">
@@ -15147,13 +15047,13 @@
         </is>
       </c>
       <c r="O34" s="15">
-        <v>12058</v>
+        <v>11389</v>
       </c>
       <c r="P34" s="15">
-        <v>22830</v>
+        <v>2142</v>
       </c>
       <c r="Q34" s="16">
-        <v>0.6</v>
+        <v>0.14</v>
       </c>
       <c r="R34" s="17" t="inlineStr">
         <is>
@@ -15162,17 +15062,17 @@
       </c>
       <c r="S34" s="18" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
       <c r="T34" s="15">
-        <v>62</v>
+        <v>117</v>
       </c>
       <c r="U34" s="16">
-        <v>-0.24</v>
+        <v>-0.08</v>
       </c>
       <c r="V34" s="15">
-        <v>9244</v>
+        <v>8891</v>
       </c>
       <c r="W34" s="15"/>
       <c r="X34" s="15"/>
@@ -15180,41 +15080,41 @@
         <v>2</v>
       </c>
       <c r="Z34" s="20">
-        <v>122.21</v>
+        <v>75.99</v>
       </c>
       <c r="AA34" s="4"/>
       <c r="AB34" s="1"/>
       <c r="AC34" s="2"/>
       <c r="AD34" s="19">
-        <v>264</v>
+        <v>582</v>
       </c>
       <c r="AE34" s="15">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AF34" s="21">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="AG34" s="22">
-        <v>0.4032</v>
+        <v>0</v>
       </c>
       <c r="AH34" s="20">
-        <v>11.13</v>
+        <v>5.21</v>
       </c>
       <c r="AI34" s="16">
-        <v>0.79</v>
+        <v>0.78</v>
       </c>
       <c r="AJ34"/>
       <c r="AK34" s="13" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="AL34" s="19">
-        <v>734</v>
+        <v>353</v>
       </c>
       <c r="AM34" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AN34" s="13"/>
@@ -15224,26 +15124,38 @@
         <v>10</v>
       </c>
       <c r="AR34" s="19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS34" s="14" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Chelsea Company Limited</t>
         </is>
       </c>
       <c r="AT34" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
-        </is>
-      </c>
-      <c r="AU34" s="13"/>
-      <c r="AV34" s="14"/>
+          <t>FBA</t>
+        </is>
+      </c>
+      <c r="AU34" s="13" t="inlineStr">
+        <is>
+          <t>CN(HK)</t>
+        </is>
+      </c>
+      <c r="AV34" s="14" t="inlineStr">
+        <is>
+          <t>Tin Hau Hong Kong 852 HK</t>
+        </is>
+      </c>
       <c r="AW34" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AUAKXO7WRPF4V</t>
-        </is>
-      </c>
-      <c r="AX34" s="13"/>
+          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3ZOAHYWM588P</t>
+        </is>
+      </c>
+      <c r="AX34" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="AY34" s="13" t="inlineStr">
         <is>
           <t>Y</t>
@@ -15257,11 +15169,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD34" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BD34" s="13"/>
       <c r="BE34" s="13"/>
       <c r="BF34" s="13"/>
       <c r="BG34" s="13"/>
@@ -15273,39 +15181,39 @@
       </c>
       <c r="BJ34" s="23" t="inlineStr">
         <is>
-          <t>11 Chilogrammi</t>
+          <t>3,4 Chilogrammi</t>
         </is>
       </c>
       <c r="BK34" s="23"/>
       <c r="BL34" s="23" t="inlineStr">
         <is>
-          <t>39,4P x 35,5l x 57H cm</t>
+          <t>28P x 22l x 28H cm</t>
         </is>
       </c>
       <c r="BM34" s="23"/>
       <c r="BN34" s="23" t="inlineStr">
         <is>
-          <t>10.54 kg</t>
+          <t>4.21 kg</t>
         </is>
       </c>
       <c r="BO34" s="23" t="inlineStr">
         <is>
-          <t>10.54 kg</t>
+          <t>4.21 kg</t>
         </is>
       </c>
       <c r="BP34" s="23" t="inlineStr">
         <is>
-          <t>61 x 39.2 x 34 cm</t>
+          <t>44.5 x 33.7 x 19.7 cm</t>
         </is>
       </c>
       <c r="BQ34" s="23" t="inlineStr">
         <is>
-          <t>61.00 x 39.20 x 34.00 cm</t>
+          <t>44.50 x 33.70 x 19.70 cm</t>
         </is>
       </c>
       <c r="BR34" s="13" t="inlineStr">
         <is>
-          <t>轻型标准大件</t>
+          <t>标准包裹</t>
         </is>
       </c>
     </row>
@@ -15316,40 +15224,40 @@
       <c r="B35" s="13"/>
       <c r="C35" s="14" t="inlineStr">
         <is>
-          <t>B0FJFDG5PY</t>
+          <t>B0DT7CPRW2</t>
         </is>
       </c>
       <c r="D35" s="14"/>
       <c r="E35" s="14"/>
       <c r="F35" s="14" t="inlineStr">
         <is>
-          <t>Akitas</t>
+          <t>Shark</t>
         </is>
       </c>
       <c r="G35" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/stores/Akitas/page/EE82F545-EF96-443C-8B75-30C504BE3C43?lp_asin=B0FJFDG5PY&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.it/stores/Shark/page/6BE84762-FC53-42E0-873B-1D7826105161?lp_asin=B0DT7CPRW2&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H35" s="14" t="inlineStr">
         <is>
-          <t>Akitas X7 600W Lavatappeti e Divani Lava e Asciuga, 14kPa Potente Aspirazione, Lava Tappezzeria per Auto, Moquette, Materassi</t>
+          <t>Shark StainStriker HairPro Pet, Pulitore con Aspirazione 450W, PX250EUTs4 Accessori, Animali Domestici, Tubo Flessibile, 2</t>
         </is>
       </c>
       <c r="I35" s="14"/>
       <c r="J35" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0FJFDG5PY?psc=1</t>
+          <t>https://www.amazon.it/dp/B0DT7CPRW2?psc=1</t>
         </is>
       </c>
       <c r="K35" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41eJu8zeBKL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/415bHD1YKaL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L35" s="14" t="inlineStr">
         <is>
-          <t>B0FJFDG5PY</t>
+          <t>B0DT7CPRW2</t>
         </is>
       </c>
       <c r="M35" s="14" t="inlineStr">
@@ -15363,13 +15271,13 @@
         </is>
       </c>
       <c r="O35" s="15">
-        <v>11389</v>
+        <v>13514</v>
       </c>
       <c r="P35" s="15">
-        <v>2142</v>
+        <v>8670</v>
       </c>
       <c r="Q35" s="16">
-        <v>0.14</v>
+        <v>0.27</v>
       </c>
       <c r="R35" s="17" t="inlineStr">
         <is>
@@ -15378,59 +15286,59 @@
       </c>
       <c r="S35" s="18" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>32</t>
         </is>
       </c>
       <c r="T35" s="15">
-        <v>117</v>
+        <v>47</v>
       </c>
       <c r="U35" s="16">
-        <v>-0.08</v>
+        <v>-0.79</v>
       </c>
       <c r="V35" s="15">
-        <v>8891</v>
+        <v>7848</v>
       </c>
       <c r="W35" s="15"/>
       <c r="X35" s="15"/>
       <c r="Y35" s="19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z35" s="20">
-        <v>75.99</v>
+        <v>136.86</v>
       </c>
       <c r="AA35" s="4"/>
       <c r="AB35" s="1"/>
       <c r="AC35" s="2"/>
       <c r="AD35" s="19">
-        <v>582</v>
+        <v>138</v>
       </c>
       <c r="AE35" s="15">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AF35" s="21">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AG35" s="22">
-        <v>0</v>
+        <v>0.19149999999999998</v>
       </c>
       <c r="AH35" s="20">
-        <v>5.21</v>
+        <v>9.35</v>
       </c>
       <c r="AI35" s="16">
-        <v>0.78</v>
+        <v>0.81</v>
       </c>
       <c r="AJ35"/>
       <c r="AK35" s="13" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="AL35" s="19">
-        <v>353</v>
+        <v>561</v>
       </c>
       <c r="AM35" s="13" t="inlineStr">
         <is>
-          <t>FBA</t>
+          <t>AMZ</t>
         </is>
       </c>
       <c r="AN35" s="13"/>
@@ -15444,34 +15352,22 @@
       </c>
       <c r="AS35" s="14" t="inlineStr">
         <is>
-          <t>Chelsea Company Limited</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="AT35" s="13" t="inlineStr">
         <is>
-          <t>FBA</t>
-        </is>
-      </c>
-      <c r="AU35" s="13" t="inlineStr">
-        <is>
-          <t>CN(HK)</t>
-        </is>
-      </c>
-      <c r="AV35" s="14" t="inlineStr">
-        <is>
-          <t>Tin Hau Hong Kong 852 HK</t>
-        </is>
-      </c>
+          <t>AMZ</t>
+        </is>
+      </c>
+      <c r="AU35" s="13"/>
+      <c r="AV35" s="14"/>
       <c r="AW35" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3ZOAHYWM588P</t>
-        </is>
-      </c>
-      <c r="AX35" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2XLKW1ZJ6I33S</t>
+        </is>
+      </c>
+      <c r="AX35" s="13"/>
       <c r="AY35" s="13" t="inlineStr">
         <is>
           <t>Y</t>
@@ -15485,7 +15381,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD35" s="13"/>
+      <c r="BD35" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BE35" s="13"/>
       <c r="BF35" s="13"/>
       <c r="BG35" s="13"/>
@@ -15497,39 +15397,39 @@
       </c>
       <c r="BJ35" s="23" t="inlineStr">
         <is>
-          <t>3,4 Chilogrammi</t>
+          <t>4,6 Chilogrammi</t>
         </is>
       </c>
       <c r="BK35" s="23"/>
       <c r="BL35" s="23" t="inlineStr">
         <is>
-          <t>28P x 22l x 28H cm</t>
+          <t>36,5P x 29,4l x 38,1H cm</t>
         </is>
       </c>
       <c r="BM35" s="23"/>
       <c r="BN35" s="23" t="inlineStr">
         <is>
-          <t>4.21 kg</t>
+          <t>6.98 kg</t>
         </is>
       </c>
       <c r="BO35" s="23" t="inlineStr">
         <is>
-          <t>4.21 kg</t>
+          <t>6.98 kg</t>
         </is>
       </c>
       <c r="BP35" s="23" t="inlineStr">
         <is>
-          <t>44.5 x 33.7 x 19.7 cm</t>
+          <t>39.4 x 35.7 x 31.4 cm</t>
         </is>
       </c>
       <c r="BQ35" s="23" t="inlineStr">
         <is>
-          <t>44.50 x 33.70 x 19.70 cm</t>
+          <t>39.40 x 35.70 x 31.40 cm</t>
         </is>
       </c>
       <c r="BR35" s="13" t="inlineStr">
         <is>
-          <t>标准包裹</t>
+          <t>轻型标准大件</t>
         </is>
       </c>
     </row>
@@ -15540,40 +15440,40 @@
       <c r="B36" s="13"/>
       <c r="C36" s="14" t="inlineStr">
         <is>
-          <t>B0DT7CPRW2</t>
+          <t>B0H97LW9DL</t>
         </is>
       </c>
       <c r="D36" s="14"/>
       <c r="E36" s="14"/>
       <c r="F36" s="14" t="inlineStr">
         <is>
-          <t>Shark</t>
+          <t>PUREBEAR</t>
         </is>
       </c>
       <c r="G36" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/stores/Shark/page/6BE84762-FC53-42E0-873B-1D7826105161?lp_asin=B0DT7CPRW2&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.it/stores/Rispostaimmediatain24ore/page/DC11DA78-3928-4F1D-8E2F-8AD84D6FF0A2?lp_asin=B0H97LW9DL&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H36" s="14" t="inlineStr">
         <is>
-          <t>Shark StainStriker HairPro Pet, Pulitore con Aspirazione 450W, PX250EUTs4 Accessori, Animali Domestici, Tubo Flessibile, 2</t>
+          <t>PUREBEAR Pulitore Tappezzeria, Lavatappeti Divani LavasLavatappeti Divani Lava | Tubo Lungo Pulizia Divano| Materasso| Sedi</t>
         </is>
       </c>
       <c r="I36" s="14"/>
       <c r="J36" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0DT7CPRW2?psc=1</t>
+          <t>https://www.amazon.it/dp/B0H97LW9DL?psc=1</t>
         </is>
       </c>
       <c r="K36" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/415bHD1YKaL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/51LnggCx6eL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L36" s="14" t="inlineStr">
         <is>
-          <t>B0DT7CPRW2</t>
+          <t>B0H97LW9DL</t>
         </is>
       </c>
       <c r="M36" s="14" t="inlineStr">
@@ -15587,13 +15487,13 @@
         </is>
       </c>
       <c r="O36" s="15">
-        <v>13514</v>
+        <v>3086</v>
       </c>
       <c r="P36" s="15">
-        <v>8670</v>
+        <v>35047</v>
       </c>
       <c r="Q36" s="16">
-        <v>0.27</v>
+        <v>0.92</v>
       </c>
       <c r="R36" s="17" t="inlineStr">
         <is>
@@ -15602,85 +15502,91 @@
       </c>
       <c r="S36" s="18" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>10</t>
         </is>
       </c>
       <c r="T36" s="15">
-        <v>47</v>
-      </c>
-      <c r="U36" s="16">
-        <v>-0.79</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="U36" s="16"/>
       <c r="V36" s="15">
-        <v>7848</v>
+        <v>7764</v>
       </c>
       <c r="W36" s="15"/>
       <c r="X36" s="15"/>
       <c r="Y36" s="19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z36" s="20">
-        <v>136.86</v>
+        <v>117.64</v>
       </c>
       <c r="AA36" s="4"/>
       <c r="AB36" s="1"/>
       <c r="AC36" s="2"/>
       <c r="AD36" s="19">
-        <v>138</v>
+        <v>20</v>
       </c>
       <c r="AE36" s="15">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AF36" s="21">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="AG36" s="22">
-        <v>0.19149999999999998</v>
+        <v>0</v>
       </c>
       <c r="AH36" s="20">
-        <v>9.35</v>
+        <v>8.9</v>
       </c>
       <c r="AI36" s="16">
-        <v>0.81</v>
+        <v>0.77</v>
       </c>
       <c r="AJ36"/>
       <c r="AK36" s="13" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="AL36" s="19">
-        <v>561</v>
+        <v>17</v>
       </c>
       <c r="AM36" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AN36" s="13"/>
       <c r="AO36" s="13"/>
       <c r="AP36" s="4"/>
       <c r="AQ36" s="19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AR36" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS36" s="14" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>MengfanchaoMLw</t>
         </is>
       </c>
       <c r="AT36" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
-        </is>
-      </c>
-      <c r="AU36" s="13"/>
-      <c r="AV36" s="14"/>
+          <t>FBA</t>
+        </is>
+      </c>
+      <c r="AU36" s="13" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="AV36" s="14" t="inlineStr">
+        <is>
+          <t>huanggangshi hubeisheng 438000 CN</t>
+        </is>
+      </c>
       <c r="AW36" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2XLKW1ZJ6I33S</t>
+          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1SGZEKAW8X162</t>
         </is>
       </c>
       <c r="AX36" s="13"/>
@@ -15713,34 +15619,34 @@
       </c>
       <c r="BJ36" s="23" t="inlineStr">
         <is>
-          <t>4,6 Chilogrammi</t>
-        </is>
-      </c>
-      <c r="BK36" s="23"/>
-      <c r="BL36" s="23" t="inlineStr">
-        <is>
-          <t>36,5P x 29,4l x 38,1H cm</t>
-        </is>
-      </c>
+          <t>4,3 Kilograms</t>
+        </is>
+      </c>
+      <c r="BK36" s="23" t="inlineStr">
+        <is>
+          <t>4.30 kg</t>
+        </is>
+      </c>
+      <c r="BL36" s="23"/>
       <c r="BM36" s="23"/>
       <c r="BN36" s="23" t="inlineStr">
         <is>
-          <t>6.98 kg</t>
+          <t>4.3 kg</t>
         </is>
       </c>
       <c r="BO36" s="23" t="inlineStr">
         <is>
-          <t>6.98 kg</t>
+          <t>4.30 kg</t>
         </is>
       </c>
       <c r="BP36" s="23" t="inlineStr">
         <is>
-          <t>39.4 x 35.7 x 31.4 cm</t>
+          <t>42 x 35 x 20 cm</t>
         </is>
       </c>
       <c r="BQ36" s="23" t="inlineStr">
         <is>
-          <t>39.40 x 35.70 x 31.40 cm</t>
+          <t>42.00 x 35.00 x 20.00 cm</t>
         </is>
       </c>
       <c r="BR36" s="13" t="inlineStr">
@@ -15756,40 +15662,40 @@
       <c r="B37" s="13"/>
       <c r="C37" s="14" t="inlineStr">
         <is>
-          <t>B0H97LW9DL</t>
+          <t>B0H4TXR27S</t>
         </is>
       </c>
       <c r="D37" s="14"/>
       <c r="E37" s="14"/>
       <c r="F37" s="14" t="inlineStr">
         <is>
-          <t>PUREBEAR</t>
+          <t>Redkey</t>
         </is>
       </c>
       <c r="G37" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/stores/Rispostaimmediatain24ore/page/DC11DA78-3928-4F1D-8E2F-8AD84D6FF0A2?lp_asin=B0H97LW9DL&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.it/stores/Redkey/page/D0F8E94D-480F-4BD7-ADC2-FEE4358EEB34?lp_asin=B0H4TXR27S&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H37" s="14" t="inlineStr">
         <is>
-          <t>PUREBEAR Pulitore Tappezzeria, Lavatappeti Divani LavasLavatappeti Divani Lava | Tubo Lungo Pulizia Divano| Materasso| Sedi</t>
+          <t>Redkey Rd-F1 Lavatappeti Lava e Asciuga, 4 in 1 Aspiratore Lava a Vapore con Aspirazione 26000Pa, 1800W Pulizia Profonda per</t>
         </is>
       </c>
       <c r="I37" s="14"/>
       <c r="J37" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0H97LW9DL?psc=1</t>
+          <t>https://www.amazon.it/dp/B0H4TXR27S?psc=1</t>
         </is>
       </c>
       <c r="K37" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/51LnggCx6eL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41f8wwTeaGL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L37" s="14" t="inlineStr">
         <is>
-          <t>B0H97LW9DL</t>
+          <t>B0H4TXR27S</t>
         </is>
       </c>
       <c r="M37" s="14" t="inlineStr">
@@ -15803,13 +15709,13 @@
         </is>
       </c>
       <c r="O37" s="15">
-        <v>3086</v>
+        <v>10557</v>
       </c>
       <c r="P37" s="15">
-        <v>35047</v>
+        <v>7587</v>
       </c>
       <c r="Q37" s="16">
-        <v>0.92</v>
+        <v>0.48</v>
       </c>
       <c r="R37" s="17" t="inlineStr">
         <is>
@@ -15818,15 +15724,15 @@
       </c>
       <c r="S37" s="18" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>25</t>
         </is>
       </c>
       <c r="T37" s="15">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="U37" s="16"/>
       <c r="V37" s="15">
-        <v>7764</v>
+        <v>7699</v>
       </c>
       <c r="W37" s="15"/>
       <c r="X37" s="15"/>
@@ -15834,83 +15740,61 @@
         <v>1</v>
       </c>
       <c r="Z37" s="20">
-        <v>117.64</v>
+        <v>139.99</v>
       </c>
       <c r="AA37" s="4"/>
       <c r="AB37" s="1"/>
       <c r="AC37" s="2"/>
-      <c r="AD37" s="19">
-        <v>20</v>
-      </c>
-      <c r="AE37" s="15">
-        <v>0</v>
-      </c>
-      <c r="AF37" s="21">
-        <v>5</v>
-      </c>
+      <c r="AD37" s="19"/>
+      <c r="AE37" s="15"/>
+      <c r="AF37" s="21"/>
       <c r="AG37" s="22">
         <v>0</v>
       </c>
       <c r="AH37" s="20">
-        <v>8.9</v>
+        <v>9.57</v>
       </c>
       <c r="AI37" s="16">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="AJ37"/>
       <c r="AK37" s="13" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AL37" s="19">
-        <v>17</v>
+        <v>83</v>
       </c>
       <c r="AM37" s="13" t="inlineStr">
         <is>
-          <t>FBA</t>
+          <t>AMZ</t>
         </is>
       </c>
       <c r="AN37" s="13"/>
       <c r="AO37" s="13"/>
       <c r="AP37" s="4"/>
       <c r="AQ37" s="19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AR37" s="19">
         <v>1</v>
       </c>
       <c r="AS37" s="14" t="inlineStr">
         <is>
-          <t>MengfanchaoMLw</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="AT37" s="13" t="inlineStr">
         <is>
-          <t>FBA</t>
-        </is>
-      </c>
-      <c r="AU37" s="13" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="AV37" s="14" t="inlineStr">
-        <is>
-          <t>huanggangshi hubeisheng 438000 CN</t>
-        </is>
-      </c>
-      <c r="AW37" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1SGZEKAW8X162</t>
-        </is>
-      </c>
+          <t>AMZ</t>
+        </is>
+      </c>
+      <c r="AU37" s="13"/>
+      <c r="AV37" s="14"/>
+      <c r="AW37" s="13"/>
       <c r="AX37" s="13"/>
-      <c r="AY37" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="AY37" s="13"/>
       <c r="AZ37" s="13"/>
       <c r="BA37" s="13"/>
       <c r="BB37" s="13"/>
@@ -15919,50 +15803,42 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD37" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BD37" s="13"/>
       <c r="BE37" s="13"/>
       <c r="BF37" s="13"/>
       <c r="BG37" s="13"/>
       <c r="BH37" s="14"/>
-      <c r="BI37" s="23" t="inlineStr">
-        <is>
-          <t>Scelta Amazon</t>
-        </is>
-      </c>
+      <c r="BI37" s="23"/>
       <c r="BJ37" s="23" t="inlineStr">
         <is>
-          <t>4,3 Kilograms</t>
+          <t>6,8 Kilograms</t>
         </is>
       </c>
       <c r="BK37" s="23" t="inlineStr">
         <is>
-          <t>4.30 kg</t>
+          <t>6.80 kg</t>
         </is>
       </c>
       <c r="BL37" s="23"/>
       <c r="BM37" s="23"/>
       <c r="BN37" s="23" t="inlineStr">
         <is>
-          <t>4.3 kg</t>
+          <t>6.8 kg</t>
         </is>
       </c>
       <c r="BO37" s="23" t="inlineStr">
         <is>
-          <t>4.30 kg</t>
+          <t>6.80 kg</t>
         </is>
       </c>
       <c r="BP37" s="23" t="inlineStr">
         <is>
-          <t>42 x 35 x 20 cm</t>
+          <t>37 x 35 x 35 cm</t>
         </is>
       </c>
       <c r="BQ37" s="23" t="inlineStr">
         <is>
-          <t>42.00 x 35.00 x 20.00 cm</t>
+          <t>37.00 x 35.00 x 35.00 cm</t>
         </is>
       </c>
       <c r="BR37" s="13" t="inlineStr">
@@ -15978,40 +15854,40 @@
       <c r="B38" s="13"/>
       <c r="C38" s="14" t="inlineStr">
         <is>
-          <t>B0H4TXR27S</t>
+          <t>B0GXVNJC4S</t>
         </is>
       </c>
       <c r="D38" s="14"/>
       <c r="E38" s="14"/>
       <c r="F38" s="14" t="inlineStr">
         <is>
-          <t>Redkey</t>
+          <t>Cecotec</t>
         </is>
       </c>
       <c r="G38" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/stores/Redkey/page/D0F8E94D-480F-4BD7-ADC2-FEE4358EEB34?lp_asin=B0H4TXR27S&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.it/Cecotec/b/ref=bl_dp_s_web_19986335031?ie=UTF8&amp;node=19986335031&amp;field-lbr_brands_browse-bin=Cecotec</t>
         </is>
       </c>
       <c r="H38" s="14" t="inlineStr">
         <is>
-          <t>Redkey Rd-F1 Lavatappeti Lava e Asciuga, 4 in 1 Aspiratore Lava a Vapore con Aspirazione 26000Pa, 1800W Pulizia Profonda per</t>
+          <t>Cecotec Pulitore aspirante per tappezzeria Conga 7000 Carpet&amp;Spot Clean Steam XXL Neo, 1700W, Pulizia 3in1, Serbatoi 1600ml a</t>
         </is>
       </c>
       <c r="I38" s="14"/>
       <c r="J38" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0H4TXR27S?psc=1</t>
+          <t>https://www.amazon.it/dp/B0GXVNJC4S?psc=1</t>
         </is>
       </c>
       <c r="K38" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41f8wwTeaGL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/81yDnM5PJYL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L38" s="14" t="inlineStr">
         <is>
-          <t>B0H4TXR27S</t>
+          <t>B0GXVNJC4S</t>
         </is>
       </c>
       <c r="M38" s="14" t="inlineStr">
@@ -16025,13 +15901,13 @@
         </is>
       </c>
       <c r="O38" s="15">
-        <v>10557</v>
+        <v>14515</v>
       </c>
       <c r="P38" s="15">
-        <v>7587</v>
+        <v>43643</v>
       </c>
       <c r="Q38" s="16">
-        <v>0.48</v>
+        <v>0.75</v>
       </c>
       <c r="R38" s="17" t="inlineStr">
         <is>
@@ -16040,30 +15916,38 @@
       </c>
       <c r="S38" s="18" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>35</t>
         </is>
       </c>
       <c r="T38" s="15">
-        <v>55</v>
-      </c>
-      <c r="U38" s="16"/>
+        <v>51</v>
+      </c>
+      <c r="U38" s="16">
+        <v>0.54</v>
+      </c>
       <c r="V38" s="15">
-        <v>7699</v>
+        <v>7594</v>
       </c>
       <c r="W38" s="15"/>
       <c r="X38" s="15"/>
       <c r="Y38" s="19">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Z38" s="20">
-        <v>139.99</v>
+        <v>148.9</v>
       </c>
       <c r="AA38" s="4"/>
       <c r="AB38" s="1"/>
       <c r="AC38" s="2"/>
-      <c r="AD38" s="19"/>
-      <c r="AE38" s="15"/>
-      <c r="AF38" s="21"/>
+      <c r="AD38" s="19">
+        <v>2</v>
+      </c>
+      <c r="AE38" s="15">
+        <v>0</v>
+      </c>
+      <c r="AF38" s="21">
+        <v>5</v>
+      </c>
       <c r="AG38" s="22">
         <v>0</v>
       </c>
@@ -16071,16 +15955,16 @@
         <v>9.57</v>
       </c>
       <c r="AI38" s="16">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="AJ38"/>
       <c r="AK38" s="13" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="AL38" s="19">
-        <v>83</v>
+        <v>132</v>
       </c>
       <c r="AM38" s="13" t="inlineStr">
         <is>
@@ -16090,9 +15974,7 @@
       <c r="AN38" s="13"/>
       <c r="AO38" s="13"/>
       <c r="AP38" s="4"/>
-      <c r="AQ38" s="19">
-        <v>8</v>
-      </c>
+      <c r="AQ38" s="19"/>
       <c r="AR38" s="19">
         <v>1</v>
       </c>
@@ -16119,7 +16001,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD38" s="13"/>
+      <c r="BD38" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BE38" s="13"/>
       <c r="BF38" s="13"/>
       <c r="BG38" s="13"/>
@@ -16127,34 +16013,42 @@
       <c r="BI38" s="23"/>
       <c r="BJ38" s="23" t="inlineStr">
         <is>
-          <t>6,8 Kilograms</t>
+          <t>4.34 kg</t>
         </is>
       </c>
       <c r="BK38" s="23" t="inlineStr">
         <is>
-          <t>6.80 kg</t>
-        </is>
-      </c>
-      <c r="BL38" s="23"/>
-      <c r="BM38" s="23"/>
+          <t>4.34 kg</t>
+        </is>
+      </c>
+      <c r="BL38" s="23" t="inlineStr">
+        <is>
+          <t>24 x 32 x 30 cm</t>
+        </is>
+      </c>
+      <c r="BM38" s="23" t="inlineStr">
+        <is>
+          <t>24.00 x 32.00 x 30.00 cm</t>
+        </is>
+      </c>
       <c r="BN38" s="23" t="inlineStr">
         <is>
-          <t>6.8 kg</t>
+          <t>5.79 kg</t>
         </is>
       </c>
       <c r="BO38" s="23" t="inlineStr">
         <is>
-          <t>6.80 kg</t>
+          <t>5.79 kg</t>
         </is>
       </c>
       <c r="BP38" s="23" t="inlineStr">
         <is>
-          <t>37 x 35 x 35 cm</t>
+          <t>41.9 x 37.6 x 29 cm</t>
         </is>
       </c>
       <c r="BQ38" s="23" t="inlineStr">
         <is>
-          <t>37.00 x 35.00 x 35.00 cm</t>
+          <t>41.90 x 37.60 x 29.00 cm</t>
         </is>
       </c>
       <c r="BR38" s="13" t="inlineStr">
@@ -16170,40 +16064,40 @@
       <c r="B39" s="13"/>
       <c r="C39" s="14" t="inlineStr">
         <is>
-          <t>B0GXVNJC4S</t>
+          <t>B0HBWJY7M3</t>
         </is>
       </c>
       <c r="D39" s="14"/>
       <c r="E39" s="14"/>
       <c r="F39" s="14" t="inlineStr">
         <is>
-          <t>Cecotec</t>
+          <t>Vacmaster</t>
         </is>
       </c>
       <c r="G39" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/Cecotec/b/ref=bl_dp_s_web_19986335031?ie=UTF8&amp;node=19986335031&amp;field-lbr_brands_browse-bin=Cecotec</t>
+          <t>https://www.amazon.it/stores/VACMASTER/page/F372FF16-5498-423D-9923-A4EFB43DC86B?lp_asin=B0HBWJY7M3&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H39" s="14" t="inlineStr">
         <is>
-          <t>Cecotec Pulitore aspirante per tappezzeria Conga 7000 Carpet&amp;Spot Clean Steam XXL Neo, 1700W, Pulizia 3in1, Serbatoi 1600ml a</t>
+          <t>Vacmaster 16Kpa Lavatessuti e LavateppetisSmacchiatore Auto &amp; Divani 500W | Spotlet pulisce come lavatessuti portatile tepp</t>
         </is>
       </c>
       <c r="I39" s="14"/>
       <c r="J39" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0GXVNJC4S?psc=1</t>
+          <t>https://www.amazon.it/dp/B0HBWJY7M3?psc=1</t>
         </is>
       </c>
       <c r="K39" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/81yDnM5PJYL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/414oCMjoraL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L39" s="14" t="inlineStr">
         <is>
-          <t>B0GXVNJC4S</t>
+          <t>B0HBWJY7M3</t>
         </is>
       </c>
       <c r="M39" s="14" t="inlineStr">
@@ -16217,13 +16111,13 @@
         </is>
       </c>
       <c r="O39" s="15">
-        <v>14515</v>
+        <v>13939</v>
       </c>
       <c r="P39" s="15">
-        <v>43643</v>
+        <v>-4499</v>
       </c>
       <c r="Q39" s="16">
-        <v>0.75</v>
+        <v>-0.48</v>
       </c>
       <c r="R39" s="17" t="inlineStr">
         <is>
@@ -16232,55 +16126,55 @@
       </c>
       <c r="S39" s="18" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>30</t>
         </is>
       </c>
       <c r="T39" s="15">
-        <v>51</v>
+        <v>119</v>
       </c>
       <c r="U39" s="16">
-        <v>0.54</v>
+        <v>1.14</v>
       </c>
       <c r="V39" s="15">
-        <v>7594</v>
+        <v>6632</v>
       </c>
       <c r="W39" s="15"/>
       <c r="X39" s="15"/>
       <c r="Y39" s="19">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Z39" s="20">
-        <v>148.9</v>
+        <v>55.73</v>
       </c>
       <c r="AA39" s="4"/>
       <c r="AB39" s="1"/>
       <c r="AC39" s="2"/>
       <c r="AD39" s="19">
-        <v>2</v>
+        <v>505</v>
       </c>
       <c r="AE39" s="15">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AF39" s="21">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="AG39" s="22">
-        <v>0</v>
+        <v>0.0756</v>
       </c>
       <c r="AH39" s="20">
-        <v>9.57</v>
+        <v>5.46</v>
       </c>
       <c r="AI39" s="16">
-        <v>0.79</v>
+        <v>0.78</v>
       </c>
       <c r="AJ39"/>
       <c r="AK39" s="13" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="AL39" s="19">
-        <v>132</v>
+        <v>37</v>
       </c>
       <c r="AM39" s="13" t="inlineStr">
         <is>
@@ -16290,7 +16184,9 @@
       <c r="AN39" s="13"/>
       <c r="AO39" s="13"/>
       <c r="AP39" s="4"/>
-      <c r="AQ39" s="19"/>
+      <c r="AQ39" s="19">
+        <v>8</v>
+      </c>
       <c r="AR39" s="19">
         <v>1</v>
       </c>
@@ -16329,47 +16225,39 @@
       <c r="BI39" s="23"/>
       <c r="BJ39" s="23" t="inlineStr">
         <is>
-          <t>4.34 kg</t>
-        </is>
-      </c>
-      <c r="BK39" s="23" t="inlineStr">
-        <is>
-          <t>4.34 kg</t>
-        </is>
-      </c>
+          <t>3,09 Chilogrammi</t>
+        </is>
+      </c>
+      <c r="BK39" s="23"/>
       <c r="BL39" s="23" t="inlineStr">
         <is>
-          <t>24 x 32 x 30 cm</t>
-        </is>
-      </c>
-      <c r="BM39" s="23" t="inlineStr">
-        <is>
-          <t>24.00 x 32.00 x 30.00 cm</t>
-        </is>
-      </c>
+          <t>32,8P x 22l x 31,5H cm</t>
+        </is>
+      </c>
+      <c r="BM39" s="23"/>
       <c r="BN39" s="23" t="inlineStr">
         <is>
-          <t>5.79 kg</t>
+          <t>3.09 kg</t>
         </is>
       </c>
       <c r="BO39" s="23" t="inlineStr">
         <is>
-          <t>5.79 kg</t>
+          <t>3.09 kg</t>
         </is>
       </c>
       <c r="BP39" s="23" t="inlineStr">
         <is>
-          <t>41.9 x 37.6 x 29 cm</t>
+          <t>32.8 x 31.5 x 22 cm</t>
         </is>
       </c>
       <c r="BQ39" s="23" t="inlineStr">
         <is>
-          <t>41.90 x 37.60 x 29.00 cm</t>
+          <t>32.80 x 31.50 x 22.00 cm</t>
         </is>
       </c>
       <c r="BR39" s="13" t="inlineStr">
         <is>
-          <t>轻型标准大件</t>
+          <t>标准包裹</t>
         </is>
       </c>
     </row>
@@ -16380,40 +16268,40 @@
       <c r="B40" s="13"/>
       <c r="C40" s="14" t="inlineStr">
         <is>
-          <t>B0HBWJY7M3</t>
+          <t>B0DJD5C46J</t>
         </is>
       </c>
       <c r="D40" s="14"/>
       <c r="E40" s="14"/>
       <c r="F40" s="14" t="inlineStr">
         <is>
-          <t>Vacmaster</t>
+          <t>Cecotec</t>
         </is>
       </c>
       <c r="G40" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/stores/VACMASTER/page/F372FF16-5498-423D-9923-A4EFB43DC86B?lp_asin=B0HBWJY7M3&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.it/Cecotec/b/ref=bl_dp_s_web_19986335031?ie=UTF8&amp;node=19986335031&amp;field-lbr_brands_browse-bin=Cecotec</t>
         </is>
       </c>
       <c r="H40" s="14" t="inlineStr">
         <is>
-          <t>Vacmaster 16Kpa Lavatessuti e LavateppetisSmacchiatore Auto &amp; Divani 500W | Spotlet pulisce come lavatessuti portatile tepp</t>
+          <t>Cecotec Aspirapolvere Lava Tappeti Conga 3000 Carpetclean, 3in1:Spruzza, Pulisce e Aspira, 400W, 2 Serbatoi - Acqua Pulita e</t>
         </is>
       </c>
       <c r="I40" s="14"/>
       <c r="J40" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0HBWJY7M3?psc=1</t>
+          <t>https://www.amazon.it/dp/B0DJD5C46J?psc=1</t>
         </is>
       </c>
       <c r="K40" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/414oCMjoraL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/715qquaM5jL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L40" s="14" t="inlineStr">
         <is>
-          <t>B0HBWJY7M3</t>
+          <t>B0DJD5C46J</t>
         </is>
       </c>
       <c r="M40" s="14" t="inlineStr">
@@ -16427,13 +16315,13 @@
         </is>
       </c>
       <c r="O40" s="15">
-        <v>13939</v>
+        <v>6063</v>
       </c>
       <c r="P40" s="15">
-        <v>-4499</v>
+        <v>95762</v>
       </c>
       <c r="Q40" s="16">
-        <v>-0.48</v>
+        <v>0.94</v>
       </c>
       <c r="R40" s="17" t="inlineStr">
         <is>
@@ -16442,85 +16330,101 @@
       </c>
       <c r="S40" s="18" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>13</t>
         </is>
       </c>
       <c r="T40" s="15">
-        <v>119</v>
+        <v>54</v>
       </c>
       <c r="U40" s="16">
-        <v>1.14</v>
+        <v>3.33</v>
       </c>
       <c r="V40" s="15">
-        <v>6632</v>
+        <v>6110</v>
       </c>
       <c r="W40" s="15"/>
       <c r="X40" s="15"/>
       <c r="Y40" s="19">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Z40" s="20">
-        <v>55.73</v>
+        <v>59.76</v>
       </c>
       <c r="AA40" s="4"/>
       <c r="AB40" s="1"/>
       <c r="AC40" s="2"/>
       <c r="AD40" s="19">
-        <v>505</v>
+        <v>333</v>
       </c>
       <c r="AE40" s="15">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="AF40" s="21">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="AG40" s="22">
-        <v>0.0756</v>
+        <v>0.3148</v>
       </c>
       <c r="AH40" s="20">
-        <v>5.46</v>
+        <v>9.12</v>
       </c>
       <c r="AI40" s="16">
-        <v>0.78</v>
+        <v>0.77</v>
       </c>
       <c r="AJ40"/>
       <c r="AK40" s="13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AL40" s="19">
-        <v>37</v>
+        <v>694</v>
       </c>
       <c r="AM40" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AN40" s="13"/>
       <c r="AO40" s="13"/>
       <c r="AP40" s="4"/>
       <c r="AQ40" s="19">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AR40" s="19">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="AS40" s="14" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>SD-Handel GmbH</t>
         </is>
       </c>
       <c r="AT40" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
-        </is>
-      </c>
-      <c r="AU40" s="13"/>
-      <c r="AV40" s="14"/>
-      <c r="AW40" s="13"/>
+          <t>FBA</t>
+        </is>
+      </c>
+      <c r="AU40" s="13" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="AV40" s="14" t="inlineStr">
+        <is>
+          <t>Grünwald 82031 DE</t>
+        </is>
+      </c>
+      <c r="AW40" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1RXW3TLJ3ZGW0</t>
+        </is>
+      </c>
       <c r="AX40" s="13"/>
-      <c r="AY40" s="13"/>
+      <c r="AY40" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="AZ40" s="13"/>
       <c r="BA40" s="13"/>
       <c r="BB40" s="13"/>
@@ -16538,42 +16442,54 @@
       <c r="BF40" s="13"/>
       <c r="BG40" s="13"/>
       <c r="BH40" s="14"/>
-      <c r="BI40" s="23"/>
+      <c r="BI40" s="23" t="inlineStr">
+        <is>
+          <t>Scelta Amazon</t>
+        </is>
+      </c>
       <c r="BJ40" s="23" t="inlineStr">
         <is>
-          <t>3,09 Chilogrammi</t>
-        </is>
-      </c>
-      <c r="BK40" s="23"/>
+          <t>3.76 kg</t>
+        </is>
+      </c>
+      <c r="BK40" s="23" t="inlineStr">
+        <is>
+          <t>3.76 kg</t>
+        </is>
+      </c>
       <c r="BL40" s="23" t="inlineStr">
         <is>
-          <t>32,8P x 22l x 31,5H cm</t>
-        </is>
-      </c>
-      <c r="BM40" s="23"/>
+          <t>37 x 25 x 36 cm</t>
+        </is>
+      </c>
+      <c r="BM40" s="23" t="inlineStr">
+        <is>
+          <t>37.00 x 25.00 x 36.00 cm</t>
+        </is>
+      </c>
       <c r="BN40" s="23" t="inlineStr">
         <is>
-          <t>3.09 kg</t>
+          <t>4.72 kg</t>
         </is>
       </c>
       <c r="BO40" s="23" t="inlineStr">
         <is>
-          <t>3.09 kg</t>
+          <t>4.72 kg</t>
         </is>
       </c>
       <c r="BP40" s="23" t="inlineStr">
         <is>
-          <t>32.8 x 31.5 x 22 cm</t>
+          <t>37.8 x 35.9 x 25.2 cm</t>
         </is>
       </c>
       <c r="BQ40" s="23" t="inlineStr">
         <is>
-          <t>32.80 x 31.50 x 22.00 cm</t>
+          <t>37.80 x 35.90 x 25.20 cm</t>
         </is>
       </c>
       <c r="BR40" s="13" t="inlineStr">
         <is>
-          <t>标准包裹</t>
+          <t>轻型标准大件</t>
         </is>
       </c>
     </row>
@@ -16584,40 +16500,40 @@
       <c r="B41" s="13"/>
       <c r="C41" s="14" t="inlineStr">
         <is>
-          <t>B0DJD5C46J</t>
+          <t>B0GDCZ7BWK</t>
         </is>
       </c>
       <c r="D41" s="14"/>
       <c r="E41" s="14"/>
       <c r="F41" s="14" t="inlineStr">
         <is>
-          <t>Cecotec</t>
+          <t>HYCHIKA BETTER TOOLS FOR BETTER LIFE</t>
         </is>
       </c>
       <c r="G41" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/Cecotec/b/ref=bl_dp_s_web_19986335031?ie=UTF8&amp;node=19986335031&amp;field-lbr_brands_browse-bin=Cecotec</t>
+          <t>https://www.amazon.it/stores/HYCHIKABETTERTOOLSFORBETTERLIFE/page/15D103CB-D5AC-4757-BA0D-C568361A5A34?lp_asin=B0GDCZ7BWK&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H41" s="14" t="inlineStr">
         <is>
-          <t>Cecotec Aspirapolvere Lava Tappeti Conga 3000 Carpetclean, 3in1:Spruzza, Pulisce e Aspira, 400W, 2 Serbatoi - Acqua Pulita e</t>
+          <t>HYCHIKA Lavatappeti e Divani Portatile 1800W, 17kPa Lava tappezzeria, Doppio Serbatoio e Autopulizia, Lavatappeti pulitore pe</t>
         </is>
       </c>
       <c r="I41" s="14"/>
       <c r="J41" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0DJD5C46J?psc=1</t>
+          <t>https://www.amazon.it/dp/B0GDCZ7BWK?psc=1</t>
         </is>
       </c>
       <c r="K41" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/715qquaM5jL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/51aWYbD9oWL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L41" s="14" t="inlineStr">
         <is>
-          <t>B0DJD5C46J</t>
+          <t>B0GDCZ7BWK</t>
         </is>
       </c>
       <c r="M41" s="14" t="inlineStr">
@@ -16631,13 +16547,13 @@
         </is>
       </c>
       <c r="O41" s="15">
-        <v>6063</v>
+        <v>13101</v>
       </c>
       <c r="P41" s="15">
-        <v>95762</v>
+        <v>-24352</v>
       </c>
       <c r="Q41" s="16">
-        <v>0.94</v>
+        <v>-0.57</v>
       </c>
       <c r="R41" s="17" t="inlineStr">
         <is>
@@ -16646,43 +16562,43 @@
       </c>
       <c r="S41" s="18" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>30</t>
         </is>
       </c>
       <c r="T41" s="15">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="U41" s="16">
-        <v>3.33</v>
+        <v>0.98</v>
       </c>
       <c r="V41" s="15">
-        <v>6110</v>
+        <v>6094</v>
       </c>
       <c r="W41" s="15"/>
       <c r="X41" s="15"/>
       <c r="Y41" s="19">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Z41" s="20">
-        <v>59.76</v>
+        <v>97.94</v>
       </c>
       <c r="AA41" s="4"/>
       <c r="AB41" s="1"/>
       <c r="AC41" s="2"/>
       <c r="AD41" s="19">
-        <v>333</v>
+        <v>206</v>
       </c>
       <c r="AE41" s="15">
-        <v>17</v>
+        <v>62</v>
       </c>
       <c r="AF41" s="21">
-        <v>4.3</v>
+        <v>3</v>
       </c>
       <c r="AG41" s="22">
-        <v>0.3148</v>
+        <v>0</v>
       </c>
       <c r="AH41" s="20">
-        <v>9.12</v>
+        <v>8.9</v>
       </c>
       <c r="AI41" s="16">
         <v>0.77</v>
@@ -16690,57 +16606,41 @@
       <c r="AJ41"/>
       <c r="AK41" s="13" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="AL41" s="19">
-        <v>694</v>
+        <v>120</v>
       </c>
       <c r="AM41" s="13" t="inlineStr">
         <is>
-          <t>FBA</t>
+          <t>AMZ</t>
         </is>
       </c>
       <c r="AN41" s="13"/>
       <c r="AO41" s="13"/>
       <c r="AP41" s="4"/>
       <c r="AQ41" s="19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AR41" s="19">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="AS41" s="14" t="inlineStr">
         <is>
-          <t>SD-Handel GmbH</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="AT41" s="13" t="inlineStr">
         <is>
-          <t>FBA</t>
-        </is>
-      </c>
-      <c r="AU41" s="13" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="AV41" s="14" t="inlineStr">
-        <is>
-          <t>Grünwald 82031 DE</t>
-        </is>
-      </c>
-      <c r="AW41" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1RXW3TLJ3ZGW0</t>
-        </is>
-      </c>
+          <t>AMZ</t>
+        </is>
+      </c>
+      <c r="AU41" s="13"/>
+      <c r="AV41" s="14"/>
+      <c r="AW41" s="13"/>
       <c r="AX41" s="13"/>
-      <c r="AY41" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="AY41" s="13"/>
       <c r="AZ41" s="13"/>
       <c r="BA41" s="13"/>
       <c r="BB41" s="13"/>
@@ -16758,49 +16658,41 @@
       <c r="BF41" s="13"/>
       <c r="BG41" s="13"/>
       <c r="BH41" s="14"/>
-      <c r="BI41" s="23" t="inlineStr">
-        <is>
-          <t>Scelta Amazon</t>
-        </is>
-      </c>
+      <c r="BI41" s="23"/>
       <c r="BJ41" s="23" t="inlineStr">
         <is>
-          <t>3.76 kg</t>
+          <t>5,49 Kilograms</t>
         </is>
       </c>
       <c r="BK41" s="23" t="inlineStr">
         <is>
-          <t>3.76 kg</t>
+          <t>5.49 kg</t>
         </is>
       </c>
       <c r="BL41" s="23" t="inlineStr">
         <is>
-          <t>37 x 25 x 36 cm</t>
-        </is>
-      </c>
-      <c r="BM41" s="23" t="inlineStr">
-        <is>
-          <t>37.00 x 25.00 x 36.00 cm</t>
-        </is>
-      </c>
+          <t>43P x 19l x 33H cm</t>
+        </is>
+      </c>
+      <c r="BM41" s="23"/>
       <c r="BN41" s="23" t="inlineStr">
         <is>
-          <t>4.72 kg</t>
+          <t>5.49 kg</t>
         </is>
       </c>
       <c r="BO41" s="23" t="inlineStr">
         <is>
-          <t>4.72 kg</t>
+          <t>5.49 kg</t>
         </is>
       </c>
       <c r="BP41" s="23" t="inlineStr">
         <is>
-          <t>37.8 x 35.9 x 25.2 cm</t>
+          <t>44.4 x 34.3 x 20.2 cm</t>
         </is>
       </c>
       <c r="BQ41" s="23" t="inlineStr">
         <is>
-          <t>37.80 x 35.90 x 25.20 cm</t>
+          <t>44.40 x 34.30 x 20.20 cm</t>
         </is>
       </c>
       <c r="BR41" s="13" t="inlineStr">
@@ -16816,40 +16708,40 @@
       <c r="B42" s="13"/>
       <c r="C42" s="14" t="inlineStr">
         <is>
-          <t>B0GDCZ7BWK</t>
+          <t>B0BPZJSXCQ</t>
         </is>
       </c>
       <c r="D42" s="14"/>
       <c r="E42" s="14"/>
       <c r="F42" s="14" t="inlineStr">
         <is>
-          <t>HYCHIKA BETTER TOOLS FOR BETTER LIFE</t>
+          <t>Cecotec</t>
         </is>
       </c>
       <c r="G42" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/stores/HYCHIKABETTERTOOLSFORBETTERLIFE/page/15D103CB-D5AC-4757-BA0D-C568361A5A34?lp_asin=B0GDCZ7BWK&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.it/Cecotec/b/ref=bl_dp_s_web_19986335031?ie=UTF8&amp;node=19986335031&amp;field-lbr_brands_browse-bin=Cecotec</t>
         </is>
       </c>
       <c r="H42" s="14" t="inlineStr">
         <is>
-          <t>HYCHIKA Lavatappeti e Divani Portatile 1800W, 17kPa Lava tappezzeria, Doppio Serbatoio e Autopulizia, Lavatappeti pulitore pe</t>
+          <t>Cecotec Aspirapolvere Lava Tappeti Conga 3000 Carpetclean, 3in1:Spruzza, Pulisce e Aspira, 400W, 2 Serbatoi - Acqua Pulita e</t>
         </is>
       </c>
       <c r="I42" s="14"/>
       <c r="J42" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0GDCZ7BWK?psc=1</t>
+          <t>https://www.amazon.it/dp/B0BPZJSXCQ?psc=1</t>
         </is>
       </c>
       <c r="K42" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/51aWYbD9oWL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41-V4acAJLL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L42" s="14" t="inlineStr">
         <is>
-          <t>B0GDCZ7BWK</t>
+          <t>B0BPZJSXCQ</t>
         </is>
       </c>
       <c r="M42" s="14" t="inlineStr">
@@ -16863,13 +16755,13 @@
         </is>
       </c>
       <c r="O42" s="15">
-        <v>13101</v>
+        <v>23369</v>
       </c>
       <c r="P42" s="15">
-        <v>-24352</v>
+        <v>-5237</v>
       </c>
       <c r="Q42" s="16">
-        <v>-0.57</v>
+        <v>-0.24</v>
       </c>
       <c r="R42" s="17" t="inlineStr">
         <is>
@@ -16878,85 +16770,101 @@
       </c>
       <c r="S42" s="18" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>42</t>
         </is>
       </c>
       <c r="T42" s="15">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="U42" s="16">
-        <v>0.98</v>
+        <v>-0.17</v>
       </c>
       <c r="V42" s="15">
-        <v>6094</v>
+        <v>5441</v>
       </c>
       <c r="W42" s="15"/>
       <c r="X42" s="15"/>
       <c r="Y42" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z42" s="20">
-        <v>97.94</v>
+        <v>72.53</v>
       </c>
       <c r="AA42" s="4"/>
       <c r="AB42" s="1"/>
       <c r="AC42" s="2"/>
       <c r="AD42" s="19">
-        <v>206</v>
+        <v>3271</v>
       </c>
       <c r="AE42" s="15">
-        <v>62</v>
+        <v>27</v>
       </c>
       <c r="AF42" s="21">
-        <v>3</v>
+        <v>4.3</v>
       </c>
       <c r="AG42" s="22">
-        <v>0</v>
+        <v>0.4286</v>
       </c>
       <c r="AH42" s="20">
         <v>8.9</v>
       </c>
       <c r="AI42" s="16">
-        <v>0.77</v>
+        <v>0.73</v>
       </c>
       <c r="AJ42"/>
       <c r="AK42" s="13" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2023-03-21</t>
         </is>
       </c>
       <c r="AL42" s="19">
-        <v>120</v>
+        <v>1268</v>
       </c>
       <c r="AM42" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
+          <t>FBM</t>
         </is>
       </c>
       <c r="AN42" s="13"/>
       <c r="AO42" s="13"/>
       <c r="AP42" s="4"/>
       <c r="AQ42" s="19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AR42" s="19">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="AS42" s="14" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Supermedia online</t>
         </is>
       </c>
       <c r="AT42" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
-        </is>
-      </c>
-      <c r="AU42" s="13"/>
-      <c r="AV42" s="14"/>
-      <c r="AW42" s="13"/>
+          <t>FBM</t>
+        </is>
+      </c>
+      <c r="AU42" s="13" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="AV42" s="14" t="inlineStr">
+        <is>
+          <t>Italia 25135 IT</t>
+        </is>
+      </c>
+      <c r="AW42" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1PTIZUJDIGRO9</t>
+        </is>
+      </c>
       <c r="AX42" s="13"/>
-      <c r="AY42" s="13"/>
+      <c r="AY42" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="AZ42" s="13"/>
       <c r="BA42" s="13"/>
       <c r="BB42" s="13"/>
@@ -16974,41 +16882,41 @@
       <c r="BF42" s="13"/>
       <c r="BG42" s="13"/>
       <c r="BH42" s="14"/>
-      <c r="BI42" s="23"/>
+      <c r="BI42" s="23" t="inlineStr">
+        <is>
+          <t>Scelta Amazon</t>
+        </is>
+      </c>
       <c r="BJ42" s="23" t="inlineStr">
         <is>
-          <t>5,49 Kilograms</t>
-        </is>
-      </c>
-      <c r="BK42" s="23" t="inlineStr">
-        <is>
-          <t>5.49 kg</t>
-        </is>
-      </c>
+          <t>3,6 Chilogrammi</t>
+        </is>
+      </c>
+      <c r="BK42" s="23"/>
       <c r="BL42" s="23" t="inlineStr">
         <is>
-          <t>43P x 19l x 33H cm</t>
+          <t>27,5P x 22l x 28,5H cm</t>
         </is>
       </c>
       <c r="BM42" s="23"/>
       <c r="BN42" s="23" t="inlineStr">
         <is>
-          <t>5.49 kg</t>
+          <t>4.85 kg</t>
         </is>
       </c>
       <c r="BO42" s="23" t="inlineStr">
         <is>
-          <t>5.49 kg</t>
+          <t>4.85 kg</t>
         </is>
       </c>
       <c r="BP42" s="23" t="inlineStr">
         <is>
-          <t>44.4 x 34.3 x 20.2 cm</t>
+          <t>35.2 x 31 x 30.5 cm</t>
         </is>
       </c>
       <c r="BQ42" s="23" t="inlineStr">
         <is>
-          <t>44.40 x 34.30 x 20.20 cm</t>
+          <t>35.20 x 31.00 x 30.50 cm</t>
         </is>
       </c>
       <c r="BR42" s="13" t="inlineStr">
@@ -17024,40 +16932,40 @@
       <c r="B43" s="13"/>
       <c r="C43" s="14" t="inlineStr">
         <is>
-          <t>B0BPZJSXCQ</t>
+          <t>B0GFF7C519</t>
         </is>
       </c>
       <c r="D43" s="14"/>
       <c r="E43" s="14"/>
       <c r="F43" s="14" t="inlineStr">
         <is>
-          <t>Cecotec</t>
+          <t>Akitas</t>
         </is>
       </c>
       <c r="G43" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/Cecotec/b/ref=bl_dp_s_web_19986335031?ie=UTF8&amp;node=19986335031&amp;field-lbr_brands_browse-bin=Cecotec</t>
+          <t>https://www.amazon.it/stores/Akitas/page/EE82F545-EF96-443C-8B75-30C504BE3C43?lp_asin=B0GFF7C519&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H43" s="14" t="inlineStr">
         <is>
-          <t>Cecotec Aspirapolvere Lava Tappeti Conga 3000 Carpetclean, 3in1:Spruzza, Pulisce e Aspira, 400W, 2 Serbatoi - Acqua Pulita e</t>
+          <t>Akitas X5 lavatappezzeria per tappeti e imbottiti, con detergente concentrato da 30 ml, doppio serbatoio, autopulizia, legger</t>
         </is>
       </c>
       <c r="I43" s="14"/>
       <c r="J43" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0BPZJSXCQ?psc=1</t>
+          <t>https://www.amazon.it/dp/B0GFF7C519?psc=1</t>
         </is>
       </c>
       <c r="K43" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41-V4acAJLL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41qPnZFK2xL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L43" s="14" t="inlineStr">
         <is>
-          <t>B0BPZJSXCQ</t>
+          <t>B0GFF7C519</t>
         </is>
       </c>
       <c r="M43" s="14" t="inlineStr">
@@ -17071,13 +16979,13 @@
         </is>
       </c>
       <c r="O43" s="15">
-        <v>23369</v>
+        <v>13468</v>
       </c>
       <c r="P43" s="15">
-        <v>-5237</v>
+        <v>83090</v>
       </c>
       <c r="Q43" s="16">
-        <v>-0.24</v>
+        <v>0.9</v>
       </c>
       <c r="R43" s="17" t="inlineStr">
         <is>
@@ -17086,17 +16994,17 @@
       </c>
       <c r="S43" s="18" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>31</t>
         </is>
       </c>
       <c r="T43" s="15">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="U43" s="16">
-        <v>-0.17</v>
+        <v>0.18</v>
       </c>
       <c r="V43" s="15">
-        <v>5441</v>
+        <v>5179</v>
       </c>
       <c r="W43" s="15"/>
       <c r="X43" s="15"/>
@@ -17104,75 +17012,73 @@
         <v>1</v>
       </c>
       <c r="Z43" s="20">
-        <v>72.53</v>
+        <v>69.99</v>
       </c>
       <c r="AA43" s="4"/>
       <c r="AB43" s="1"/>
       <c r="AC43" s="2"/>
       <c r="AD43" s="19">
-        <v>3271</v>
+        <v>183</v>
       </c>
       <c r="AE43" s="15">
-        <v>27</v>
+        <v>87</v>
       </c>
       <c r="AF43" s="21">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AG43" s="22">
-        <v>0.4286</v>
+        <v>0</v>
       </c>
       <c r="AH43" s="20">
-        <v>8.9</v>
+        <v>5.43</v>
       </c>
       <c r="AI43" s="16">
-        <v>0.73</v>
+        <v>0.76</v>
       </c>
       <c r="AJ43"/>
       <c r="AK43" s="13" t="inlineStr">
         <is>
-          <t>2023-03-21</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="AL43" s="19">
-        <v>1268</v>
+        <v>230</v>
       </c>
       <c r="AM43" s="13" t="inlineStr">
         <is>
-          <t>FBM</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AN43" s="13"/>
       <c r="AO43" s="13"/>
       <c r="AP43" s="4"/>
-      <c r="AQ43" s="19">
-        <v>10</v>
-      </c>
+      <c r="AQ43" s="19"/>
       <c r="AR43" s="19">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="AS43" s="14" t="inlineStr">
         <is>
-          <t>Supermedia online</t>
+          <t>Chelsea Company Limited</t>
         </is>
       </c>
       <c r="AT43" s="13" t="inlineStr">
         <is>
-          <t>FBM</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AU43" s="13" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>CN(HK)</t>
         </is>
       </c>
       <c r="AV43" s="14" t="inlineStr">
         <is>
-          <t>Italia 25135 IT</t>
+          <t>Tin Hau Hong Kong 852 HK</t>
         </is>
       </c>
       <c r="AW43" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1PTIZUJDIGRO9</t>
+          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3ZOAHYWM588P</t>
         </is>
       </c>
       <c r="AX43" s="13"/>
@@ -17205,39 +17111,43 @@
       </c>
       <c r="BJ43" s="23" t="inlineStr">
         <is>
-          <t>3,6 Chilogrammi</t>
-        </is>
-      </c>
-      <c r="BK43" s="23"/>
+          <t>3,2 Kilograms</t>
+        </is>
+      </c>
+      <c r="BK43" s="23" t="inlineStr">
+        <is>
+          <t>3.20 kg</t>
+        </is>
+      </c>
       <c r="BL43" s="23" t="inlineStr">
         <is>
-          <t>27,5P x 22l x 28,5H cm</t>
+          <t>36P x 22l x 28H cm</t>
         </is>
       </c>
       <c r="BM43" s="23"/>
       <c r="BN43" s="23" t="inlineStr">
         <is>
-          <t>4.85 kg</t>
+          <t>3.2 kg</t>
         </is>
       </c>
       <c r="BO43" s="23" t="inlineStr">
         <is>
-          <t>4.85 kg</t>
+          <t>3.20 kg</t>
         </is>
       </c>
       <c r="BP43" s="23" t="inlineStr">
         <is>
-          <t>35.2 x 31 x 30.5 cm</t>
+          <t>34.5 x 27.9 x 19.4 cm</t>
         </is>
       </c>
       <c r="BQ43" s="23" t="inlineStr">
         <is>
-          <t>35.20 x 31.00 x 30.50 cm</t>
+          <t>34.50 x 27.90 x 19.40 cm</t>
         </is>
       </c>
       <c r="BR43" s="13" t="inlineStr">
         <is>
-          <t>轻型标准大件</t>
+          <t>标准包裹</t>
         </is>
       </c>
     </row>
@@ -17248,40 +17158,40 @@
       <c r="B44" s="13"/>
       <c r="C44" s="14" t="inlineStr">
         <is>
-          <t>B0GFF7C519</t>
+          <t>B0H3KVMBCH</t>
         </is>
       </c>
       <c r="D44" s="14"/>
       <c r="E44" s="14"/>
       <c r="F44" s="14" t="inlineStr">
         <is>
-          <t>Akitas</t>
+          <t>MELLWIN</t>
         </is>
       </c>
       <c r="G44" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/stores/Akitas/page/EE82F545-EF96-443C-8B75-30C504BE3C43?lp_asin=B0GFF7C519&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=MELLWIN</t>
         </is>
       </c>
       <c r="H44" s="14" t="inlineStr">
         <is>
-          <t>Akitas X5 lavatappezzeria per tappeti e imbottiti, con detergente concentrato da 30 ml, doppio serbatoio, autopulizia, legger</t>
+          <t>MELLWIN lava tappezzeria vapore e riscaldamento,18 kPa,Riscaldamento rapidospulitore tappezzeria da 1250 W Proprietari di a</t>
         </is>
       </c>
       <c r="I44" s="14"/>
       <c r="J44" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0GFF7C519?psc=1</t>
+          <t>https://www.amazon.it/dp/B0H3KVMBCH?psc=1</t>
         </is>
       </c>
       <c r="K44" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41qPnZFK2xL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41W3WF+EhbL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L44" s="14" t="inlineStr">
         <is>
-          <t>B0GFF7C519</t>
+          <t>B0H3KVMBCH</t>
         </is>
       </c>
       <c r="M44" s="14" t="inlineStr">
@@ -17295,13 +17205,13 @@
         </is>
       </c>
       <c r="O44" s="15">
-        <v>13468</v>
+        <v>23084</v>
       </c>
       <c r="P44" s="15">
-        <v>83090</v>
+        <v>-16252</v>
       </c>
       <c r="Q44" s="16">
-        <v>0.9</v>
+        <v>-0.65</v>
       </c>
       <c r="R44" s="17" t="inlineStr">
         <is>
@@ -17310,17 +17220,15 @@
       </c>
       <c r="S44" s="18" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>46</t>
         </is>
       </c>
       <c r="T44" s="15">
-        <v>74</v>
-      </c>
-      <c r="U44" s="16">
-        <v>0.18</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="U44" s="16"/>
       <c r="V44" s="15">
-        <v>5179</v>
+        <v>4522</v>
       </c>
       <c r="W44" s="15"/>
       <c r="X44" s="15"/>
@@ -17328,37 +17236,37 @@
         <v>1</v>
       </c>
       <c r="Z44" s="20">
-        <v>69.99</v>
+        <v>118.99</v>
       </c>
       <c r="AA44" s="4"/>
       <c r="AB44" s="1"/>
       <c r="AC44" s="2"/>
       <c r="AD44" s="19">
-        <v>183</v>
+        <v>3</v>
       </c>
       <c r="AE44" s="15">
-        <v>87</v>
+        <v>1</v>
       </c>
       <c r="AF44" s="21">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AG44" s="22">
-        <v>0</v>
+        <v>0.0263</v>
       </c>
       <c r="AH44" s="20">
-        <v>5.43</v>
+        <v>5.46</v>
       </c>
       <c r="AI44" s="16">
-        <v>0.76</v>
+        <v>0.79</v>
       </c>
       <c r="AJ44"/>
       <c r="AK44" s="13" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AL44" s="19">
-        <v>230</v>
+        <v>32</v>
       </c>
       <c r="AM44" s="13" t="inlineStr">
         <is>
@@ -17368,13 +17276,15 @@
       <c r="AN44" s="13"/>
       <c r="AO44" s="13"/>
       <c r="AP44" s="4"/>
-      <c r="AQ44" s="19"/>
+      <c r="AQ44" s="19">
+        <v>8</v>
+      </c>
       <c r="AR44" s="19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AS44" s="14" t="inlineStr">
         <is>
-          <t>Chelsea Company Limited</t>
+          <t>EUROAPEX LANDING</t>
         </is>
       </c>
       <c r="AT44" s="13" t="inlineStr">
@@ -17384,25 +17294,21 @@
       </c>
       <c r="AU44" s="13" t="inlineStr">
         <is>
-          <t>CN(HK)</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="AV44" s="14" t="inlineStr">
         <is>
-          <t>Tin Hau Hong Kong 852 HK</t>
+          <t>DOLNOŚLĄSKIE 53-332 PL</t>
         </is>
       </c>
       <c r="AW44" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3ZOAHYWM588P</t>
+          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=ABSTVEQNNON26</t>
         </is>
       </c>
       <c r="AX44" s="13"/>
-      <c r="AY44" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="AY44" s="13"/>
       <c r="AZ44" s="13"/>
       <c r="BA44" s="13"/>
       <c r="BB44" s="13"/>
@@ -17420,45 +17326,41 @@
       <c r="BF44" s="13"/>
       <c r="BG44" s="13"/>
       <c r="BH44" s="14"/>
-      <c r="BI44" s="23" t="inlineStr">
-        <is>
-          <t>Scelta Amazon</t>
-        </is>
-      </c>
+      <c r="BI44" s="23"/>
       <c r="BJ44" s="23" t="inlineStr">
         <is>
-          <t>3,2 Kilograms</t>
-        </is>
-      </c>
-      <c r="BK44" s="23" t="inlineStr">
-        <is>
-          <t>3.20 kg</t>
-        </is>
-      </c>
+          <t>4 Chilogrammi</t>
+        </is>
+      </c>
+      <c r="BK44" s="23"/>
       <c r="BL44" s="23" t="inlineStr">
         <is>
-          <t>36P x 22l x 28H cm</t>
-        </is>
-      </c>
-      <c r="BM44" s="23"/>
+          <t>43 x 19 x 32 cm</t>
+        </is>
+      </c>
+      <c r="BM44" s="23" t="inlineStr">
+        <is>
+          <t>43.00 x 19.00 x 32.00 cm</t>
+        </is>
+      </c>
       <c r="BN44" s="23" t="inlineStr">
         <is>
-          <t>3.2 kg</t>
+          <t>4 kg</t>
         </is>
       </c>
       <c r="BO44" s="23" t="inlineStr">
         <is>
-          <t>3.20 kg</t>
+          <t>4.00 kg</t>
         </is>
       </c>
       <c r="BP44" s="23" t="inlineStr">
         <is>
-          <t>34.5 x 27.9 x 19.4 cm</t>
+          <t>43 x 32 x 19 cm</t>
         </is>
       </c>
       <c r="BQ44" s="23" t="inlineStr">
         <is>
-          <t>34.50 x 27.90 x 19.40 cm</t>
+          <t>43.00 x 32.00 x 19.00 cm</t>
         </is>
       </c>
       <c r="BR44" s="13" t="inlineStr">
@@ -17474,40 +17376,40 @@
       <c r="B45" s="13"/>
       <c r="C45" s="14" t="inlineStr">
         <is>
-          <t>B0H3KVMBCH</t>
+          <t>B0FXX52XPP</t>
         </is>
       </c>
       <c r="D45" s="14"/>
       <c r="E45" s="14"/>
       <c r="F45" s="14" t="inlineStr">
         <is>
-          <t>MELLWIN</t>
+          <t>Polti</t>
         </is>
       </c>
       <c r="G45" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=MELLWIN</t>
+          <t>https://www.amazon.it/stores/POLTI/page/79293619-D61E-4C36-99D5-4729A55252D6?lp_asin=B0FXX52XPP&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H45" s="14" t="inlineStr">
         <is>
-          <t>MELLWIN lava tappezzeria vapore e riscaldamento,18 kPa,Riscaldamento rapidospulitore tappezzeria da 1250 W Proprietari di a</t>
+          <t>Polti StainOver SC20, Lavatappeti a Vapore per Rimuovere le Macchie, 2000 Ws4 in 1, Smacchiatore con Funzione Vaporetto, Te</t>
         </is>
       </c>
       <c r="I45" s="14"/>
       <c r="J45" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0H3KVMBCH?psc=1</t>
+          <t>https://www.amazon.it/dp/B0FXX52XPP?psc=1</t>
         </is>
       </c>
       <c r="K45" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41W3WF+EhbL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T2/images/I/31Smsdr+waL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L45" s="14" t="inlineStr">
         <is>
-          <t>B0H3KVMBCH</t>
+          <t>B0FXX52XPP</t>
         </is>
       </c>
       <c r="M45" s="14" t="inlineStr">
@@ -17521,13 +17423,13 @@
         </is>
       </c>
       <c r="O45" s="15">
-        <v>23084</v>
+        <v>17036</v>
       </c>
       <c r="P45" s="15">
-        <v>-16252</v>
+        <v>1460</v>
       </c>
       <c r="Q45" s="16">
-        <v>-0.65</v>
+        <v>0.01</v>
       </c>
       <c r="R45" s="17" t="inlineStr">
         <is>
@@ -17536,15 +17438,17 @@
       </c>
       <c r="S45" s="18" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>41</t>
         </is>
       </c>
       <c r="T45" s="15">
-        <v>38</v>
-      </c>
-      <c r="U45" s="16"/>
+        <v>18</v>
+      </c>
+      <c r="U45" s="16">
+        <v>-0.47</v>
+      </c>
       <c r="V45" s="15">
-        <v>4522</v>
+        <v>4482</v>
       </c>
       <c r="W45" s="15"/>
       <c r="X45" s="15"/>
@@ -17552,77 +17456,65 @@
         <v>1</v>
       </c>
       <c r="Z45" s="20">
-        <v>118.99</v>
+        <v>249</v>
       </c>
       <c r="AA45" s="4"/>
       <c r="AB45" s="1"/>
       <c r="AC45" s="2"/>
       <c r="AD45" s="19">
+        <v>12</v>
+      </c>
+      <c r="AE45" s="15">
         <v>3</v>
       </c>
-      <c r="AE45" s="15">
-        <v>1</v>
-      </c>
       <c r="AF45" s="21">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AG45" s="22">
-        <v>0.0263</v>
+        <v>0.16670000000000001</v>
       </c>
       <c r="AH45" s="20">
-        <v>5.46</v>
+        <v>10.02</v>
       </c>
       <c r="AI45" s="16">
-        <v>0.79</v>
+        <v>0.82</v>
       </c>
       <c r="AJ45"/>
       <c r="AK45" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="AL45" s="19">
-        <v>32</v>
+        <v>209</v>
       </c>
       <c r="AM45" s="13" t="inlineStr">
         <is>
-          <t>FBA</t>
+          <t>AMZ</t>
         </is>
       </c>
       <c r="AN45" s="13"/>
       <c r="AO45" s="13"/>
       <c r="AP45" s="4"/>
       <c r="AQ45" s="19">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AR45" s="19">
         <v>1</v>
       </c>
       <c r="AS45" s="14" t="inlineStr">
         <is>
-          <t>EUROAPEX LANDING</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="AT45" s="13" t="inlineStr">
         <is>
-          <t>FBA</t>
-        </is>
-      </c>
-      <c r="AU45" s="13" t="inlineStr">
-        <is>
-          <t>PL</t>
-        </is>
-      </c>
-      <c r="AV45" s="14" t="inlineStr">
-        <is>
-          <t>DOLNOŚLĄSKIE 53-332 PL</t>
-        </is>
-      </c>
-      <c r="AW45" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=ABSTVEQNNON26</t>
-        </is>
-      </c>
+          <t>AMZ</t>
+        </is>
+      </c>
+      <c r="AU45" s="13"/>
+      <c r="AV45" s="14"/>
+      <c r="AW45" s="13"/>
       <c r="AX45" s="13"/>
       <c r="AY45" s="13"/>
       <c r="AZ45" s="13"/>
@@ -17645,43 +17537,43 @@
       <c r="BI45" s="23"/>
       <c r="BJ45" s="23" t="inlineStr">
         <is>
-          <t>4 Chilogrammi</t>
-        </is>
-      </c>
-      <c r="BK45" s="23"/>
+          <t>7,98 Kilograms</t>
+        </is>
+      </c>
+      <c r="BK45" s="23" t="inlineStr">
+        <is>
+          <t>7.98 kg</t>
+        </is>
+      </c>
       <c r="BL45" s="23" t="inlineStr">
         <is>
-          <t>43 x 19 x 32 cm</t>
-        </is>
-      </c>
-      <c r="BM45" s="23" t="inlineStr">
-        <is>
-          <t>43.00 x 19.00 x 32.00 cm</t>
-        </is>
-      </c>
+          <t>39P x 24l x 33H cm</t>
+        </is>
+      </c>
+      <c r="BM45" s="23"/>
       <c r="BN45" s="23" t="inlineStr">
         <is>
-          <t>4 kg</t>
+          <t>7.98 kg</t>
         </is>
       </c>
       <c r="BO45" s="23" t="inlineStr">
         <is>
-          <t>4.00 kg</t>
+          <t>7.98 kg</t>
         </is>
       </c>
       <c r="BP45" s="23" t="inlineStr">
         <is>
-          <t>43 x 32 x 19 cm</t>
+          <t>47.7 x 39.6 x 29.2 cm</t>
         </is>
       </c>
       <c r="BQ45" s="23" t="inlineStr">
         <is>
-          <t>43.00 x 32.00 x 19.00 cm</t>
+          <t>47.70 x 39.60 x 29.20 cm</t>
         </is>
       </c>
       <c r="BR45" s="13" t="inlineStr">
         <is>
-          <t>标准包裹</t>
+          <t>轻型标准大件</t>
         </is>
       </c>
     </row>
@@ -17692,40 +17584,40 @@
       <c r="B46" s="13"/>
       <c r="C46" s="14" t="inlineStr">
         <is>
-          <t>B0FXX52XPP</t>
+          <t>B0H7C5V7MZ</t>
         </is>
       </c>
       <c r="D46" s="14"/>
       <c r="E46" s="14"/>
       <c r="F46" s="14" t="inlineStr">
         <is>
-          <t>Polti</t>
+          <t>VacniQ</t>
         </is>
       </c>
       <c r="G46" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/stores/POLTI/page/79293619-D61E-4C36-99D5-4729A55252D6?lp_asin=B0FXX52XPP&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.it/stores/aspirapolvereabatteria/page/F0D8BDB2-BD7B-4C1C-9C40-2225E4C1C262?lp_asin=B0H7C5V7MZ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H46" s="14" t="inlineStr">
         <is>
-          <t>Polti StainOver SC20, Lavatappeti a Vapore per Rimuovere le Macchie, 2000 Ws4 in 1, Smacchiatore con Funzione Vaporetto, Te</t>
+          <t>VacniQ C688 Aspirapolvere lavante 4 in 1, 25000 Pa, 1800 W. Riscaldamento, disinfezione, display LED e avvisi vocali. Ideale</t>
         </is>
       </c>
       <c r="I46" s="14"/>
       <c r="J46" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0FXX52XPP?psc=1</t>
+          <t>https://www.amazon.it/dp/B0H7C5V7MZ?psc=1</t>
         </is>
       </c>
       <c r="K46" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T2/images/I/31Smsdr+waL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41cQk55jQqL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L46" s="14" t="inlineStr">
         <is>
-          <t>B0FXX52XPP</t>
+          <t>B0H7C5V7MZ</t>
         </is>
       </c>
       <c r="M46" s="14" t="inlineStr">
@@ -17739,13 +17631,13 @@
         </is>
       </c>
       <c r="O46" s="15">
-        <v>17036</v>
+        <v>23771</v>
       </c>
       <c r="P46" s="15">
-        <v>1460</v>
+        <v>41532</v>
       </c>
       <c r="Q46" s="16">
-        <v>0.01</v>
+        <v>0.66</v>
       </c>
       <c r="R46" s="17" t="inlineStr">
         <is>
@@ -17754,17 +17646,15 @@
       </c>
       <c r="S46" s="18" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>45</t>
         </is>
       </c>
       <c r="T46" s="15">
-        <v>18</v>
-      </c>
-      <c r="U46" s="16">
-        <v>-0.47</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="U46" s="16"/>
       <c r="V46" s="15">
-        <v>4482</v>
+        <v>3360</v>
       </c>
       <c r="W46" s="15"/>
       <c r="X46" s="15"/>
@@ -17772,41 +17662,41 @@
         <v>1</v>
       </c>
       <c r="Z46" s="20">
-        <v>249</v>
+        <v>139.99</v>
       </c>
       <c r="AA46" s="4"/>
       <c r="AB46" s="1"/>
       <c r="AC46" s="2"/>
       <c r="AD46" s="19">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AE46" s="15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AF46" s="21">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="AG46" s="22">
-        <v>0.16670000000000001</v>
+        <v>0.20829999999999999</v>
       </c>
       <c r="AH46" s="20">
-        <v>10.02</v>
+        <v>5.49</v>
       </c>
       <c r="AI46" s="16">
-        <v>0.82</v>
+        <v>0.81</v>
       </c>
       <c r="AJ46"/>
       <c r="AK46" s="13" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="AL46" s="19">
-        <v>209</v>
+        <v>67</v>
       </c>
       <c r="AM46" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
+          <t>FBM</t>
         </is>
       </c>
       <c r="AN46" s="13"/>
@@ -17820,17 +17710,29 @@
       </c>
       <c r="AS46" s="14" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Guevel David Commerce</t>
         </is>
       </c>
       <c r="AT46" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
-        </is>
-      </c>
-      <c r="AU46" s="13"/>
-      <c r="AV46" s="14"/>
-      <c r="AW46" s="13"/>
+          <t>FBM</t>
+        </is>
+      </c>
+      <c r="AU46" s="13" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="AV46" s="14" t="inlineStr">
+        <is>
+          <t>Paris 75002 FR</t>
+        </is>
+      </c>
+      <c r="AW46" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A97DWD1P7ED3E</t>
+        </is>
+      </c>
       <c r="AX46" s="13"/>
       <c r="AY46" s="13"/>
       <c r="AZ46" s="13"/>
@@ -17841,11 +17743,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD46" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BD46" s="13"/>
       <c r="BE46" s="13"/>
       <c r="BF46" s="13"/>
       <c r="BG46" s="13"/>
@@ -17853,43 +17751,39 @@
       <c r="BI46" s="23"/>
       <c r="BJ46" s="23" t="inlineStr">
         <is>
-          <t>7,98 Kilograms</t>
+          <t>6 Kilograms</t>
         </is>
       </c>
       <c r="BK46" s="23" t="inlineStr">
         <is>
-          <t>7.98 kg</t>
-        </is>
-      </c>
-      <c r="BL46" s="23" t="inlineStr">
-        <is>
-          <t>39P x 24l x 33H cm</t>
-        </is>
-      </c>
+          <t>6.00 kg</t>
+        </is>
+      </c>
+      <c r="BL46" s="23"/>
       <c r="BM46" s="23"/>
       <c r="BN46" s="23" t="inlineStr">
         <is>
-          <t>7.98 kg</t>
+          <t>6 kg</t>
         </is>
       </c>
       <c r="BO46" s="23" t="inlineStr">
         <is>
-          <t>7.98 kg</t>
+          <t>6.00 kg</t>
         </is>
       </c>
       <c r="BP46" s="23" t="inlineStr">
         <is>
-          <t>47.7 x 39.6 x 29.2 cm</t>
+          <t>44 x 32 x 26 cm</t>
         </is>
       </c>
       <c r="BQ46" s="23" t="inlineStr">
         <is>
-          <t>47.70 x 39.60 x 29.20 cm</t>
+          <t>44.00 x 32.00 x 26.00 cm</t>
         </is>
       </c>
       <c r="BR46" s="13" t="inlineStr">
         <is>
-          <t>轻型标准大件</t>
+          <t>标准包裹</t>
         </is>
       </c>
     </row>
@@ -17900,40 +17794,40 @@
       <c r="B47" s="13"/>
       <c r="C47" s="14" t="inlineStr">
         <is>
-          <t>B0H7C5V7MZ</t>
+          <t>B0F9PLL56G</t>
         </is>
       </c>
       <c r="D47" s="14"/>
       <c r="E47" s="14"/>
       <c r="F47" s="14" t="inlineStr">
         <is>
-          <t>VacniQ</t>
+          <t>Vax</t>
         </is>
       </c>
       <c r="G47" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/stores/aspirapolvereabatteria/page/F0D8BDB2-BD7B-4C1C-9C40-2225E4C1C262?lp_asin=B0H7C5V7MZ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.it/Vax/b/ref=bl_dp_s_web_16065939031?ie=UTF8&amp;node=16065939031&amp;field-lbr_brands_browse-bin=Vax</t>
         </is>
       </c>
       <c r="H47" s="14" t="inlineStr">
         <is>
-          <t>VacniQ C688 Aspirapolvere lavante 4 in 1, 25000 Pa, 1800 W. Riscaldamento, disinfezione, display LED e avvisi vocali. Ideale</t>
+          <t>Vax SpotWash Max Pet-Design Spot Cleaner, potente smacchiatore per tappeti e tappezzeria con tecnologia SpinScrub, serbatoio</t>
         </is>
       </c>
       <c r="I47" s="14"/>
       <c r="J47" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0H7C5V7MZ?psc=1</t>
+          <t>https://www.amazon.it/dp/B0F9PLL56G?psc=1</t>
         </is>
       </c>
       <c r="K47" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41cQk55jQqL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T4/images/I/419W+KsIGaL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L47" s="14" t="inlineStr">
         <is>
-          <t>B0H7C5V7MZ</t>
+          <t>B0F9PLL56G</t>
         </is>
       </c>
       <c r="M47" s="14" t="inlineStr">
@@ -17947,13 +17841,13 @@
         </is>
       </c>
       <c r="O47" s="15">
-        <v>23771</v>
+        <v>46736</v>
       </c>
       <c r="P47" s="15">
-        <v>41532</v>
+        <v>12925</v>
       </c>
       <c r="Q47" s="16">
-        <v>0.66</v>
+        <v>0.09</v>
       </c>
       <c r="R47" s="17" t="inlineStr">
         <is>
@@ -17962,95 +17856,77 @@
       </c>
       <c r="S47" s="18" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>56</t>
         </is>
       </c>
       <c r="T47" s="15">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="U47" s="16"/>
       <c r="V47" s="15">
-        <v>3360</v>
+        <v>2850</v>
       </c>
       <c r="W47" s="15"/>
       <c r="X47" s="15"/>
       <c r="Y47" s="19">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Z47" s="20">
-        <v>139.99</v>
+        <v>122.94</v>
       </c>
       <c r="AA47" s="4"/>
       <c r="AB47" s="1"/>
       <c r="AC47" s="2"/>
       <c r="AD47" s="19">
-        <v>7</v>
+        <v>61</v>
       </c>
       <c r="AE47" s="15">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AF47" s="21">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="AG47" s="22">
-        <v>0.20829999999999999</v>
-      </c>
-      <c r="AH47" s="20">
-        <v>5.49</v>
-      </c>
+        <v>0.15789999999999998</v>
+      </c>
+      <c r="AH47" s="20"/>
       <c r="AI47" s="16">
-        <v>0.81</v>
+        <v>0</v>
       </c>
       <c r="AJ47"/>
-      <c r="AK47" s="13" t="inlineStr">
-        <is>
-          <t>2026-07-04</t>
-        </is>
-      </c>
-      <c r="AL47" s="19">
-        <v>67</v>
-      </c>
+      <c r="AK47" s="13"/>
+      <c r="AL47" s="19"/>
       <c r="AM47" s="13" t="inlineStr">
         <is>
-          <t>FBM</t>
+          <t>AMZ</t>
         </is>
       </c>
       <c r="AN47" s="13"/>
       <c r="AO47" s="13"/>
       <c r="AP47" s="4"/>
-      <c r="AQ47" s="19">
-        <v>10</v>
-      </c>
+      <c r="AQ47" s="19"/>
       <c r="AR47" s="19">
         <v>1</v>
       </c>
       <c r="AS47" s="14" t="inlineStr">
         <is>
-          <t>Guevel David Commerce</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="AT47" s="13" t="inlineStr">
         <is>
-          <t>FBM</t>
-        </is>
-      </c>
-      <c r="AU47" s="13" t="inlineStr">
-        <is>
-          <t>FR</t>
-        </is>
-      </c>
-      <c r="AV47" s="14" t="inlineStr">
-        <is>
-          <t>Paris 75002 FR</t>
-        </is>
-      </c>
-      <c r="AW47" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A97DWD1P7ED3E</t>
-        </is>
-      </c>
+          <t>AMZ</t>
+        </is>
+      </c>
+      <c r="AU47" s="13"/>
+      <c r="AV47" s="14"/>
+      <c r="AW47" s="13"/>
       <c r="AX47" s="13"/>
-      <c r="AY47" s="13"/>
+      <c r="AY47" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="AZ47" s="13"/>
       <c r="BA47" s="13"/>
       <c r="BB47" s="13"/>
@@ -18059,49 +17935,41 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD47" s="13"/>
+      <c r="BD47" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BE47" s="13"/>
       <c r="BF47" s="13"/>
       <c r="BG47" s="13"/>
       <c r="BH47" s="14"/>
-      <c r="BI47" s="23"/>
+      <c r="BI47" s="23" t="inlineStr">
+        <is>
+          <t>Scelta Amazon</t>
+        </is>
+      </c>
       <c r="BJ47" s="23" t="inlineStr">
         <is>
-          <t>6 Kilograms</t>
+          <t>5,5 Kilograms</t>
         </is>
       </c>
       <c r="BK47" s="23" t="inlineStr">
         <is>
-          <t>6.00 kg</t>
-        </is>
-      </c>
-      <c r="BL47" s="23"/>
+          <t>5.50 kg</t>
+        </is>
+      </c>
+      <c r="BL47" s="23" t="inlineStr">
+        <is>
+          <t>28P x 38l x 40,6H cm</t>
+        </is>
+      </c>
       <c r="BM47" s="23"/>
-      <c r="BN47" s="23" t="inlineStr">
-        <is>
-          <t>6 kg</t>
-        </is>
-      </c>
-      <c r="BO47" s="23" t="inlineStr">
-        <is>
-          <t>6.00 kg</t>
-        </is>
-      </c>
-      <c r="BP47" s="23" t="inlineStr">
-        <is>
-          <t>44 x 32 x 26 cm</t>
-        </is>
-      </c>
-      <c r="BQ47" s="23" t="inlineStr">
-        <is>
-          <t>44.00 x 32.00 x 26.00 cm</t>
-        </is>
-      </c>
-      <c r="BR47" s="13" t="inlineStr">
-        <is>
-          <t>标准包裹</t>
-        </is>
-      </c>
+      <c r="BN47" s="23"/>
+      <c r="BO47" s="23"/>
+      <c r="BP47" s="23"/>
+      <c r="BQ47" s="23"/>
+      <c r="BR47" s="13"/>
     </row>
     <row r="48" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="13">
@@ -18110,40 +17978,40 @@
       <c r="B48" s="13"/>
       <c r="C48" s="14" t="inlineStr">
         <is>
-          <t>B0F9PLL56G</t>
+          <t>B0H263J8GJ</t>
         </is>
       </c>
       <c r="D48" s="14"/>
       <c r="E48" s="14"/>
       <c r="F48" s="14" t="inlineStr">
         <is>
-          <t>Vax</t>
+          <t>Hearten</t>
         </is>
       </c>
       <c r="G48" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/Vax/b/ref=bl_dp_s_web_16065939031?ie=UTF8&amp;node=16065939031&amp;field-lbr_brands_browse-bin=Vax</t>
+          <t>https://www.amazon.it/stores/Hearten/page/91157C36-9CCC-4DA6-833F-59782FACE3E0?lp_asin=B0H263J8GJ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H48" s="14" t="inlineStr">
         <is>
-          <t>Vax SpotWash Max Pet-Design Spot Cleaner, potente smacchiatore per tappeti e tappezzeria con tecnologia SpinScrub, serbatoio</t>
+          <t>Hearten Lavatappeti Portatile, Aspirazione da 22kPa, con Auto-PuliziasLava Tappezzeria, 1.5L Serbatoio, Design Compatto, Ac</t>
         </is>
       </c>
       <c r="I48" s="14"/>
       <c r="J48" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0F9PLL56G?psc=1</t>
+          <t>https://www.amazon.it/dp/B0H263J8GJ?psc=1</t>
         </is>
       </c>
       <c r="K48" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T4/images/I/419W+KsIGaL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/4163ZUVBqYL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L48" s="14" t="inlineStr">
         <is>
-          <t>B0F9PLL56G</t>
+          <t>B0H263J8GJ</t>
         </is>
       </c>
       <c r="M48" s="14" t="inlineStr">
@@ -18157,13 +18025,11 @@
         </is>
       </c>
       <c r="O48" s="15">
-        <v>46736</v>
-      </c>
-      <c r="P48" s="15">
-        <v>12925</v>
-      </c>
+        <v>11131</v>
+      </c>
+      <c r="P48" s="15"/>
       <c r="Q48" s="16">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="R48" s="17" t="inlineStr">
         <is>
@@ -18172,77 +18038,95 @@
       </c>
       <c r="S48" s="18" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>27</t>
         </is>
       </c>
       <c r="T48" s="15">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="U48" s="16"/>
       <c r="V48" s="15">
-        <v>2850</v>
+        <v>2340</v>
       </c>
       <c r="W48" s="15"/>
       <c r="X48" s="15"/>
       <c r="Y48" s="19">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Z48" s="20">
-        <v>122.94</v>
+        <v>89.99</v>
       </c>
       <c r="AA48" s="4"/>
       <c r="AB48" s="1"/>
       <c r="AC48" s="2"/>
       <c r="AD48" s="19">
-        <v>61</v>
+        <v>2</v>
       </c>
       <c r="AE48" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF48" s="21">
-        <v>4.3</v>
+        <v>3.4</v>
       </c>
       <c r="AG48" s="22">
-        <v>0.15789999999999998</v>
-      </c>
-      <c r="AH48" s="20"/>
+        <v>0.07690000000000001</v>
+      </c>
+      <c r="AH48" s="20">
+        <v>5.46</v>
+      </c>
       <c r="AI48" s="16">
-        <v>0</v>
+        <v>0.79</v>
       </c>
       <c r="AJ48"/>
-      <c r="AK48" s="13"/>
-      <c r="AL48" s="19"/>
+      <c r="AK48" s="13" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AL48" s="19">
+        <v>15</v>
+      </c>
       <c r="AM48" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AN48" s="13"/>
       <c r="AO48" s="13"/>
       <c r="AP48" s="4"/>
-      <c r="AQ48" s="19"/>
+      <c r="AQ48" s="19">
+        <v>9</v>
+      </c>
       <c r="AR48" s="19">
         <v>1</v>
       </c>
       <c r="AS48" s="14" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Hearten Direct</t>
         </is>
       </c>
       <c r="AT48" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
-        </is>
-      </c>
-      <c r="AU48" s="13"/>
-      <c r="AV48" s="14"/>
-      <c r="AW48" s="13"/>
+          <t>FBA</t>
+        </is>
+      </c>
+      <c r="AU48" s="13" t="inlineStr">
+        <is>
+          <t>CN(HK)</t>
+        </is>
+      </c>
+      <c r="AV48" s="14" t="inlineStr">
+        <is>
+          <t>Hong Kong 999077 HK</t>
+        </is>
+      </c>
+      <c r="AW48" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AGFI912YUQRG6</t>
+        </is>
+      </c>
       <c r="AX48" s="13"/>
-      <c r="AY48" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="AY48" s="13"/>
       <c r="AZ48" s="13"/>
       <c r="BA48" s="13"/>
       <c r="BB48" s="13"/>
@@ -18260,32 +18144,44 @@
       <c r="BF48" s="13"/>
       <c r="BG48" s="13"/>
       <c r="BH48" s="14"/>
-      <c r="BI48" s="23" t="inlineStr">
-        <is>
-          <t>Scelta Amazon</t>
-        </is>
-      </c>
+      <c r="BI48" s="23"/>
       <c r="BJ48" s="23" t="inlineStr">
         <is>
-          <t>5,5 Kilograms</t>
-        </is>
-      </c>
-      <c r="BK48" s="23" t="inlineStr">
-        <is>
-          <t>5.50 kg</t>
-        </is>
-      </c>
+          <t>2,5 Chilogrammi</t>
+        </is>
+      </c>
+      <c r="BK48" s="23"/>
       <c r="BL48" s="23" t="inlineStr">
         <is>
-          <t>28P x 38l x 40,6H cm</t>
+          <t>23,2P x 29,9l x 17,3H cm</t>
         </is>
       </c>
       <c r="BM48" s="23"/>
-      <c r="BN48" s="23"/>
-      <c r="BO48" s="23"/>
-      <c r="BP48" s="23"/>
-      <c r="BQ48" s="23"/>
-      <c r="BR48" s="13"/>
+      <c r="BN48" s="23" t="inlineStr">
+        <is>
+          <t>3.34 kg</t>
+        </is>
+      </c>
+      <c r="BO48" s="23" t="inlineStr">
+        <is>
+          <t>3.34 kg</t>
+        </is>
+      </c>
+      <c r="BP48" s="23" t="inlineStr">
+        <is>
+          <t>32.4 x 32.2 x 19.4 cm</t>
+        </is>
+      </c>
+      <c r="BQ48" s="23" t="inlineStr">
+        <is>
+          <t>32.40 x 32.20 x 19.40 cm</t>
+        </is>
+      </c>
+      <c r="BR48" s="13" t="inlineStr">
+        <is>
+          <t>标准包裹</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="13">
@@ -18294,40 +18190,40 @@
       <c r="B49" s="13"/>
       <c r="C49" s="14" t="inlineStr">
         <is>
-          <t>B0H263J8GJ</t>
+          <t>B0DX2J6DW2</t>
         </is>
       </c>
       <c r="D49" s="14"/>
       <c r="E49" s="14"/>
       <c r="F49" s="14" t="inlineStr">
         <is>
-          <t>Hearten</t>
+          <t>Akitas</t>
         </is>
       </c>
       <c r="G49" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/stores/Hearten/page/91157C36-9CCC-4DA6-833F-59782FACE3E0?lp_asin=B0H263J8GJ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.it/stores/Akitas/page/EE82F545-EF96-443C-8B75-30C504BE3C43?lp_asin=B0DX2J6DW2&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H49" s="14" t="inlineStr">
         <is>
-          <t>Hearten Lavatappeti Portatile, Aspirazione da 22kPa, con Auto-PuliziasLava Tappezzeria, 1.5L Serbatoio, Design Compatto, Ac</t>
+          <t>Akitas Detergente per Tappeti 1L Schiuma Ridotta Profumo Floreale Per Divani Moquette Auto Compatibile con Lavamoquette Rimuo</t>
         </is>
       </c>
       <c r="I49" s="14"/>
       <c r="J49" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0H263J8GJ?psc=1</t>
+          <t>https://www.amazon.it/dp/B0DX2J6DW2?psc=1</t>
         </is>
       </c>
       <c r="K49" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/4163ZUVBqYL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41DlwHQxtaL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L49" s="14" t="inlineStr">
         <is>
-          <t>B0H263J8GJ</t>
+          <t>B0DX2J6DW2</t>
         </is>
       </c>
       <c r="M49" s="14" t="inlineStr">
@@ -18341,11 +18237,13 @@
         </is>
       </c>
       <c r="O49" s="15">
-        <v>11131</v>
-      </c>
-      <c r="P49" s="15"/>
+        <v>38695</v>
+      </c>
+      <c r="P49" s="15">
+        <v>83090</v>
+      </c>
       <c r="Q49" s="16">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="R49" s="17" t="inlineStr">
         <is>
@@ -18354,15 +18252,17 @@
       </c>
       <c r="S49" s="18" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>49</t>
         </is>
       </c>
       <c r="T49" s="15">
-        <v>26</v>
-      </c>
-      <c r="U49" s="16"/>
+        <v>74</v>
+      </c>
+      <c r="U49" s="16">
+        <v>0.18</v>
+      </c>
       <c r="V49" s="15">
-        <v>2340</v>
+        <v>1479</v>
       </c>
       <c r="W49" s="15"/>
       <c r="X49" s="15"/>
@@ -18370,37 +18270,37 @@
         <v>1</v>
       </c>
       <c r="Z49" s="20">
-        <v>89.99</v>
+        <v>19.99</v>
       </c>
       <c r="AA49" s="4"/>
       <c r="AB49" s="1"/>
       <c r="AC49" s="2"/>
       <c r="AD49" s="19">
-        <v>2</v>
+        <v>159</v>
       </c>
       <c r="AE49" s="15">
-        <v>2</v>
+        <v>87</v>
       </c>
       <c r="AF49" s="21">
-        <v>3.4</v>
+        <v>4.7</v>
       </c>
       <c r="AG49" s="22">
-        <v>0.07690000000000001</v>
+        <v>0</v>
       </c>
       <c r="AH49" s="20">
-        <v>5.46</v>
+        <v>5.19</v>
       </c>
       <c r="AI49" s="16">
-        <v>0.79</v>
+        <v>0.56</v>
       </c>
       <c r="AJ49"/>
       <c r="AK49" s="13" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="AL49" s="19">
-        <v>15</v>
+        <v>412</v>
       </c>
       <c r="AM49" s="13" t="inlineStr">
         <is>
@@ -18411,14 +18311,14 @@
       <c r="AO49" s="13"/>
       <c r="AP49" s="4"/>
       <c r="AQ49" s="19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AR49" s="19">
         <v>1</v>
       </c>
       <c r="AS49" s="14" t="inlineStr">
         <is>
-          <t>Hearten Direct</t>
+          <t>Chelsea Company Limited</t>
         </is>
       </c>
       <c r="AT49" s="13" t="inlineStr">
@@ -18433,16 +18333,20 @@
       </c>
       <c r="AV49" s="14" t="inlineStr">
         <is>
-          <t>Hong Kong 999077 HK</t>
+          <t>Tin Hau Hong Kong 852 HK</t>
         </is>
       </c>
       <c r="AW49" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AGFI912YUQRG6</t>
+          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3ZOAHYWM588P</t>
         </is>
       </c>
       <c r="AX49" s="13"/>
-      <c r="AY49" s="13"/>
+      <c r="AY49" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="AZ49" s="13"/>
       <c r="BA49" s="13"/>
       <c r="BB49" s="13"/>
@@ -18451,503 +18355,53 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD49" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BD49" s="13"/>
       <c r="BE49" s="13"/>
       <c r="BF49" s="13"/>
       <c r="BG49" s="13"/>
       <c r="BH49" s="14"/>
-      <c r="BI49" s="23"/>
+      <c r="BI49" s="23" t="inlineStr">
+        <is>
+          <t>Scelta Amazon</t>
+        </is>
+      </c>
       <c r="BJ49" s="23" t="inlineStr">
         <is>
-          <t>2,5 Chilogrammi</t>
-        </is>
-      </c>
-      <c r="BK49" s="23"/>
+          <t>1,1 Kilograms</t>
+        </is>
+      </c>
+      <c r="BK49" s="23" t="inlineStr">
+        <is>
+          <t>1.10 kg</t>
+        </is>
+      </c>
       <c r="BL49" s="23" t="inlineStr">
         <is>
-          <t>23,2P x 29,9l x 17,3H cm</t>
+          <t>36P x 22l x 28H cm</t>
         </is>
       </c>
       <c r="BM49" s="23"/>
       <c r="BN49" s="23" t="inlineStr">
         <is>
-          <t>3.34 kg</t>
+          <t>1.13 kg</t>
         </is>
       </c>
       <c r="BO49" s="23" t="inlineStr">
         <is>
-          <t>3.34 kg</t>
+          <t>1.13 kg</t>
         </is>
       </c>
       <c r="BP49" s="23" t="inlineStr">
         <is>
-          <t>32.4 x 32.2 x 19.4 cm</t>
+          <t>23.8 x 8 x 7.5 cm</t>
         </is>
       </c>
       <c r="BQ49" s="23" t="inlineStr">
         <is>
-          <t>32.40 x 32.20 x 19.40 cm</t>
+          <t>23.80 x 8.00 x 7.50 cm</t>
         </is>
       </c>
       <c r="BR49" s="13" t="inlineStr">
-        <is>
-          <t>标准包裹</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="13">
-        <v>49</v>
-      </c>
-      <c r="B50" s="13"/>
-      <c r="C50" s="14" t="inlineStr">
-        <is>
-          <t>B086Q46MMD</t>
-        </is>
-      </c>
-      <c r="D50" s="14"/>
-      <c r="E50" s="14"/>
-      <c r="F50" s="14" t="inlineStr">
-        <is>
-          <t>STANHOME</t>
-        </is>
-      </c>
-      <c r="G50" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.it/stores/STANHOME/page/CF140807-E9D9-4EE4-98E8-28F83571D17F?lp_asin=B086Q46MMD&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
-        </is>
-      </c>
-      <c r="H50" s="14" t="inlineStr">
-        <is>
-          <t>STANHOMEsDetergente Smacchiante Tappeti Carpet Cleaner, 500 ML, Pulisce e Smacchia i Tessuti d'Arredamento</t>
-        </is>
-      </c>
-      <c r="I50" s="14"/>
-      <c r="J50" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.it/dp/B086Q46MMD?psc=1</t>
-        </is>
-      </c>
-      <c r="K50" s="14" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/31hUTFxCzpL._AC_US600_.jpg</t>
-        </is>
-      </c>
-      <c r="L50" s="14" t="inlineStr">
-        <is>
-          <t>B086Q46MMD</t>
-        </is>
-      </c>
-      <c r="M50" s="14" t="inlineStr">
-        <is>
-          <t>Casa e cucina:Aspirapolvere e pulizia di pavimenti e finestre:Lavatappeti</t>
-        </is>
-      </c>
-      <c r="N50" s="14" t="inlineStr">
-        <is>
-          <t>Visualizza i Top 100 nella categoria Casa e c</t>
-        </is>
-      </c>
-      <c r="O50" s="15">
-        <v>16011</v>
-      </c>
-      <c r="P50" s="15">
-        <v>-3906</v>
-      </c>
-      <c r="Q50" s="16">
-        <v>-0.32</v>
-      </c>
-      <c r="R50" s="17" t="inlineStr">
-        <is>
-          <t>Lavatappeti</t>
-        </is>
-      </c>
-      <c r="S50" s="18" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="T50" s="15">
-        <v>124</v>
-      </c>
-      <c r="U50" s="16">
-        <v>0</v>
-      </c>
-      <c r="V50" s="15">
-        <v>1860</v>
-      </c>
-      <c r="W50" s="15" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="X50" s="15">
-        <v>750</v>
-      </c>
-      <c r="Y50" s="19">
-        <v>1</v>
-      </c>
-      <c r="Z50" s="20">
-        <v>15</v>
-      </c>
-      <c r="AA50" s="4"/>
-      <c r="AB50" s="1"/>
-      <c r="AC50" s="2"/>
-      <c r="AD50" s="19">
-        <v>73</v>
-      </c>
-      <c r="AE50" s="15">
-        <v>3</v>
-      </c>
-      <c r="AF50" s="21">
-        <v>4.4</v>
-      </c>
-      <c r="AG50" s="22">
-        <v>0.0242</v>
-      </c>
-      <c r="AH50" s="20">
-        <v>3.74</v>
-      </c>
-      <c r="AI50" s="16">
-        <v>0.6</v>
-      </c>
-      <c r="AJ50"/>
-      <c r="AK50" s="13" t="inlineStr">
-        <is>
-          <t>2020-05-09</t>
-        </is>
-      </c>
-      <c r="AL50" s="19">
-        <v>2314</v>
-      </c>
-      <c r="AM50" s="13" t="inlineStr">
-        <is>
-          <t>FBA</t>
-        </is>
-      </c>
-      <c r="AN50" s="13"/>
-      <c r="AO50" s="13"/>
-      <c r="AP50" s="4"/>
-      <c r="AQ50" s="19">
-        <v>8</v>
-      </c>
-      <c r="AR50" s="19">
-        <v>1</v>
-      </c>
-      <c r="AS50" s="14" t="inlineStr">
-        <is>
-          <t>Stanhome S.p.A</t>
-        </is>
-      </c>
-      <c r="AT50" s="13" t="inlineStr">
-        <is>
-          <t>FBA</t>
-        </is>
-      </c>
-      <c r="AU50" s="13" t="inlineStr">
-        <is>
-          <t>IT</t>
-        </is>
-      </c>
-      <c r="AV50" s="14" t="inlineStr">
-        <is>
-          <t>ITALIA 25038 IT</t>
-        </is>
-      </c>
-      <c r="AW50" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1FKDALFGWQLQF</t>
-        </is>
-      </c>
-      <c r="AX50" s="13"/>
-      <c r="AY50" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="AZ50" s="13"/>
-      <c r="BA50" s="13"/>
-      <c r="BB50" s="13"/>
-      <c r="BC50" s="13"/>
-      <c r="BD50" s="13"/>
-      <c r="BE50" s="13"/>
-      <c r="BF50" s="13"/>
-      <c r="BG50" s="13"/>
-      <c r="BH50" s="14"/>
-      <c r="BI50" s="23" t="inlineStr">
-        <is>
-          <t>Scelta Amazon</t>
-        </is>
-      </c>
-      <c r="BJ50" s="23" t="inlineStr">
-        <is>
-          <t>550 grammi</t>
-        </is>
-      </c>
-      <c r="BK50" s="23" t="inlineStr">
-        <is>
-          <t>550.00 g</t>
-        </is>
-      </c>
-      <c r="BL50" s="23" t="inlineStr">
-        <is>
-          <t>6,7 x 24 x 6,7 cm</t>
-        </is>
-      </c>
-      <c r="BM50" s="23" t="inlineStr">
-        <is>
-          <t>6.70 x 24.00 x 6.70 cm</t>
-        </is>
-      </c>
-      <c r="BN50" s="23" t="inlineStr">
-        <is>
-          <t>550 g</t>
-        </is>
-      </c>
-      <c r="BO50" s="23" t="inlineStr">
-        <is>
-          <t>550.00 g</t>
-        </is>
-      </c>
-      <c r="BP50" s="23" t="inlineStr">
-        <is>
-          <t>23.7 x 6.1 x 6 cm</t>
-        </is>
-      </c>
-      <c r="BQ50" s="23" t="inlineStr">
-        <is>
-          <t>23.70 x 6.10 x 6.00 cm</t>
-        </is>
-      </c>
-      <c r="BR50" s="13" t="inlineStr">
-        <is>
-          <t>超大号信封</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="13">
-        <v>50</v>
-      </c>
-      <c r="B51" s="13"/>
-      <c r="C51" s="14" t="inlineStr">
-        <is>
-          <t>B0DX2J6DW2</t>
-        </is>
-      </c>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51" s="14" t="inlineStr">
-        <is>
-          <t>Akitas</t>
-        </is>
-      </c>
-      <c r="G51" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.it/stores/Akitas/page/EE82F545-EF96-443C-8B75-30C504BE3C43?lp_asin=B0DX2J6DW2&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
-        </is>
-      </c>
-      <c r="H51" s="14" t="inlineStr">
-        <is>
-          <t>Akitas Detergente per Tappeti 1L Schiuma Ridotta Profumo Floreale Per Divani Moquette Auto Compatibile con Lavamoquette Rimuo</t>
-        </is>
-      </c>
-      <c r="I51" s="14"/>
-      <c r="J51" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.it/dp/B0DX2J6DW2?psc=1</t>
-        </is>
-      </c>
-      <c r="K51" s="14" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/41DlwHQxtaL._AC_US600_.jpg</t>
-        </is>
-      </c>
-      <c r="L51" s="14" t="inlineStr">
-        <is>
-          <t>B0DX2J6DW2</t>
-        </is>
-      </c>
-      <c r="M51" s="14" t="inlineStr">
-        <is>
-          <t>Casa e cucina:Aspirapolvere e pulizia di pavimenti e finestre:Lavatappeti</t>
-        </is>
-      </c>
-      <c r="N51" s="14" t="inlineStr">
-        <is>
-          <t>Visualizza i Top 100 nella categoria Casa e c</t>
-        </is>
-      </c>
-      <c r="O51" s="15">
-        <v>38695</v>
-      </c>
-      <c r="P51" s="15">
-        <v>83090</v>
-      </c>
-      <c r="Q51" s="16">
-        <v>0.9</v>
-      </c>
-      <c r="R51" s="17" t="inlineStr">
-        <is>
-          <t>Lavatappeti</t>
-        </is>
-      </c>
-      <c r="S51" s="18" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="T51" s="15">
-        <v>74</v>
-      </c>
-      <c r="U51" s="16">
-        <v>0.18</v>
-      </c>
-      <c r="V51" s="15">
-        <v>1479</v>
-      </c>
-      <c r="W51" s="15"/>
-      <c r="X51" s="15"/>
-      <c r="Y51" s="19">
-        <v>1</v>
-      </c>
-      <c r="Z51" s="20">
-        <v>19.99</v>
-      </c>
-      <c r="AA51" s="4"/>
-      <c r="AB51" s="1"/>
-      <c r="AC51" s="2"/>
-      <c r="AD51" s="19">
-        <v>159</v>
-      </c>
-      <c r="AE51" s="15">
-        <v>87</v>
-      </c>
-      <c r="AF51" s="21">
-        <v>4.7</v>
-      </c>
-      <c r="AG51" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH51" s="20">
-        <v>5.19</v>
-      </c>
-      <c r="AI51" s="16">
-        <v>0.56</v>
-      </c>
-      <c r="AJ51"/>
-      <c r="AK51" s="13" t="inlineStr">
-        <is>
-          <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AL51" s="19">
-        <v>412</v>
-      </c>
-      <c r="AM51" s="13" t="inlineStr">
-        <is>
-          <t>FBA</t>
-        </is>
-      </c>
-      <c r="AN51" s="13"/>
-      <c r="AO51" s="13"/>
-      <c r="AP51" s="4"/>
-      <c r="AQ51" s="19">
-        <v>10</v>
-      </c>
-      <c r="AR51" s="19">
-        <v>1</v>
-      </c>
-      <c r="AS51" s="14" t="inlineStr">
-        <is>
-          <t>Chelsea Company Limited</t>
-        </is>
-      </c>
-      <c r="AT51" s="13" t="inlineStr">
-        <is>
-          <t>FBA</t>
-        </is>
-      </c>
-      <c r="AU51" s="13" t="inlineStr">
-        <is>
-          <t>CN(HK)</t>
-        </is>
-      </c>
-      <c r="AV51" s="14" t="inlineStr">
-        <is>
-          <t>Tin Hau Hong Kong 852 HK</t>
-        </is>
-      </c>
-      <c r="AW51" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3ZOAHYWM588P</t>
-        </is>
-      </c>
-      <c r="AX51" s="13"/>
-      <c r="AY51" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="AZ51" s="13"/>
-      <c r="BA51" s="13"/>
-      <c r="BB51" s="13"/>
-      <c r="BC51" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD51" s="13"/>
-      <c r="BE51" s="13"/>
-      <c r="BF51" s="13"/>
-      <c r="BG51" s="13"/>
-      <c r="BH51" s="14"/>
-      <c r="BI51" s="23" t="inlineStr">
-        <is>
-          <t>Scelta Amazon</t>
-        </is>
-      </c>
-      <c r="BJ51" s="23" t="inlineStr">
-        <is>
-          <t>1,1 Kilograms</t>
-        </is>
-      </c>
-      <c r="BK51" s="23" t="inlineStr">
-        <is>
-          <t>1.10 kg</t>
-        </is>
-      </c>
-      <c r="BL51" s="23" t="inlineStr">
-        <is>
-          <t>36P x 22l x 28H cm</t>
-        </is>
-      </c>
-      <c r="BM51" s="23"/>
-      <c r="BN51" s="23" t="inlineStr">
-        <is>
-          <t>1.13 kg</t>
-        </is>
-      </c>
-      <c r="BO51" s="23" t="inlineStr">
-        <is>
-          <t>1.13 kg</t>
-        </is>
-      </c>
-      <c r="BP51" s="23" t="inlineStr">
-        <is>
-          <t>23.8 x 8 x 7.5 cm</t>
-        </is>
-      </c>
-      <c r="BQ51" s="23" t="inlineStr">
-        <is>
-          <t>23.80 x 8.00 x 7.50 cm</t>
-        </is>
-      </c>
-      <c r="BR51" s="13" t="inlineStr">
         <is>
           <t>小包裹</t>
         </is>
@@ -19154,189 +18608,174 @@
     <hyperlink ref="M28" r:id="rId195" tooltip="https://www.amazon.it/b?node=733005031"/>
     <hyperlink ref="N28" r:id="rId196"/>
     <hyperlink ref="AW28" r:id="rId197" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2KISR7QA7WRPG"/>
-    <hyperlink ref="C29" r:id="rId198" tooltip="https://www.amazon.it/dp/B0753NXDPR"/>
-    <hyperlink ref="G29" r:id="rId199" tooltip="https://www.amazon.it/stores/BISSELL/page/EDA95B6C-7064-466B-BACA-347C73A9A423?lp_asin=B0753NXDPR&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J29" r:id="rId200" tooltip="https://www.amazon.it/dp/B0753NXDPR?psc=1"/>
-    <hyperlink ref="K29" r:id="rId201" tooltip="https://m.media-amazon.com/images/I/31BhvLWbbNL._AC_US600_.jpg"/>
-    <hyperlink ref="L29" r:id="rId202" tooltip="https://www.amazon.it/dp/B0753NXDPR"/>
-    <hyperlink ref="M29" r:id="rId203" tooltip="https://www.amazon.it/b?node=28122080031"/>
+    <hyperlink ref="C29" r:id="rId198" tooltip="https://www.amazon.it/dp/B0BSHCQQ4W"/>
+    <hyperlink ref="G29" r:id="rId199" tooltip="https://www.amazon.it/stores/HKoenig/page/978AEC1C-8AF0-4DD0-AECD-D6014C0418DD?lp_asin=B0BSHCQQ4W&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J29" r:id="rId200" tooltip="https://www.amazon.it/dp/B0BSHCQQ4W?psc=1"/>
+    <hyperlink ref="K29" r:id="rId201" tooltip="https://images-na.ssl-images-amazon.com/images/I/61W1ckv75YL._AC_US600_.jpg"/>
+    <hyperlink ref="L29" r:id="rId202" tooltip="https://www.amazon.it/dp/B0BSHCQQ4W"/>
+    <hyperlink ref="M29" r:id="rId203" tooltip="https://www.amazon.it/b?node=733005031"/>
     <hyperlink ref="N29" r:id="rId204"/>
-    <hyperlink ref="C30" r:id="rId205" tooltip="https://www.amazon.it/dp/B0BSHCQQ4W"/>
-    <hyperlink ref="G30" r:id="rId206" tooltip="https://www.amazon.it/stores/HKoenig/page/978AEC1C-8AF0-4DD0-AECD-D6014C0418DD?lp_asin=B0BSHCQQ4W&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J30" r:id="rId207" tooltip="https://www.amazon.it/dp/B0BSHCQQ4W?psc=1"/>
-    <hyperlink ref="K30" r:id="rId208" tooltip="https://images-na.ssl-images-amazon.com/images/I/61W1ckv75YL._AC_US600_.jpg"/>
-    <hyperlink ref="L30" r:id="rId209" tooltip="https://www.amazon.it/dp/B0BSHCQQ4W"/>
-    <hyperlink ref="M30" r:id="rId210" tooltip="https://www.amazon.it/b?node=733005031"/>
-    <hyperlink ref="N30" r:id="rId211"/>
-    <hyperlink ref="AW30" r:id="rId212" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2J1ZXSJG29176"/>
-    <hyperlink ref="C31" r:id="rId213" tooltip="https://www.amazon.it/dp/B0D2HFLM1C"/>
-    <hyperlink ref="G31" r:id="rId214" tooltip="https://www.amazon.it/stores/HAUSHOF/page/9EE9CFD0-E18C-46CA-98BB-FA1050DF3283?lp_asin=B0D2HFLM1C&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J31" r:id="rId215" tooltip="https://www.amazon.it/dp/B0D2HFLM1C?psc=1"/>
-    <hyperlink ref="K31" r:id="rId216" tooltip="https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T4/images/I/414TgmW8eiL._AC_US600_.jpg"/>
-    <hyperlink ref="L31" r:id="rId217" tooltip="https://www.amazon.it/dp/B0D2HFLM1C"/>
+    <hyperlink ref="AW29" r:id="rId205" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2J1ZXSJG29176"/>
+    <hyperlink ref="C30" r:id="rId206" tooltip="https://www.amazon.it/dp/B0D2HFLM1C"/>
+    <hyperlink ref="G30" r:id="rId207" tooltip="https://www.amazon.it/stores/HAUSHOF/page/9EE9CFD0-E18C-46CA-98BB-FA1050DF3283?lp_asin=B0D2HFLM1C&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J30" r:id="rId208" tooltip="https://www.amazon.it/dp/B0D2HFLM1C?psc=1"/>
+    <hyperlink ref="K30" r:id="rId209" tooltip="https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T4/images/I/414TgmW8eiL._AC_US600_.jpg"/>
+    <hyperlink ref="L30" r:id="rId210" tooltip="https://www.amazon.it/dp/B0D2HFLM1C"/>
+    <hyperlink ref="M30" r:id="rId211" tooltip="https://www.amazon.it/b?node=733005031"/>
+    <hyperlink ref="N30" r:id="rId212"/>
+    <hyperlink ref="C31" r:id="rId213" tooltip="https://www.amazon.it/dp/B0GH6TBJVW"/>
+    <hyperlink ref="G31" r:id="rId214" tooltip="https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Kitcanis"/>
+    <hyperlink ref="J31" r:id="rId215" tooltip="https://www.amazon.it/dp/B0GH6TBJVW?psc=1"/>
+    <hyperlink ref="K31" r:id="rId216" tooltip="https://m.media-amazon.com/images/I/51LdyRohTNL._AC_US600_.jpg"/>
+    <hyperlink ref="L31" r:id="rId217" tooltip="https://www.amazon.it/dp/B0GH6TBJVW"/>
     <hyperlink ref="M31" r:id="rId218" tooltip="https://www.amazon.it/b?node=733005031"/>
     <hyperlink ref="N31" r:id="rId219"/>
-    <hyperlink ref="C32" r:id="rId220" tooltip="https://www.amazon.it/dp/B0GH6TBJVW"/>
-    <hyperlink ref="G32" r:id="rId221" tooltip="https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Kitcanis"/>
-    <hyperlink ref="J32" r:id="rId222" tooltip="https://www.amazon.it/dp/B0GH6TBJVW?psc=1"/>
-    <hyperlink ref="K32" r:id="rId223" tooltip="https://m.media-amazon.com/images/I/51LdyRohTNL._AC_US600_.jpg"/>
-    <hyperlink ref="L32" r:id="rId224" tooltip="https://www.amazon.it/dp/B0GH6TBJVW"/>
-    <hyperlink ref="M32" r:id="rId225" tooltip="https://www.amazon.it/b?node=733005031"/>
-    <hyperlink ref="N32" r:id="rId226"/>
-    <hyperlink ref="AW32" r:id="rId227" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3SC5MLKO5B7LX"/>
-    <hyperlink ref="C33" r:id="rId228" tooltip="https://www.amazon.it/dp/B0FHB8RB8F"/>
-    <hyperlink ref="G33" r:id="rId229" tooltip="https://www.amazon.it/Cecotec/b/ref=bl_dp_s_web_19986335031?ie=UTF8&amp;node=19986335031&amp;field-lbr_brands_browse-bin=Cecotec"/>
-    <hyperlink ref="J33" r:id="rId230" tooltip="https://www.amazon.it/dp/B0FHB8RB8F?psc=1"/>
-    <hyperlink ref="K33" r:id="rId231" tooltip="https://m.media-amazon.com/images/I/411-YObj2pL._AC_US600_.jpg"/>
-    <hyperlink ref="L33" r:id="rId232" tooltip="https://www.amazon.it/dp/B0FHB8RB8F"/>
+    <hyperlink ref="AW31" r:id="rId220" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3SC5MLKO5B7LX"/>
+    <hyperlink ref="C32" r:id="rId221" tooltip="https://www.amazon.it/dp/B0FHB8RB8F"/>
+    <hyperlink ref="G32" r:id="rId222" tooltip="https://www.amazon.it/Cecotec/b/ref=bl_dp_s_web_19986335031?ie=UTF8&amp;node=19986335031&amp;field-lbr_brands_browse-bin=Cecotec"/>
+    <hyperlink ref="J32" r:id="rId223" tooltip="https://www.amazon.it/dp/B0FHB8RB8F?psc=1"/>
+    <hyperlink ref="K32" r:id="rId224" tooltip="https://m.media-amazon.com/images/I/411-YObj2pL._AC_US600_.jpg"/>
+    <hyperlink ref="L32" r:id="rId225" tooltip="https://www.amazon.it/dp/B0FHB8RB8F"/>
+    <hyperlink ref="M32" r:id="rId226" tooltip="https://www.amazon.it/b?node=733005031"/>
+    <hyperlink ref="N32" r:id="rId227"/>
+    <hyperlink ref="C33" r:id="rId228" tooltip="https://www.amazon.it/dp/B0DFLYY2H7"/>
+    <hyperlink ref="G33" r:id="rId229" tooltip="https://www.amazon.it/stores/VACMASTER/page/F372FF16-5498-423D-9923-A4EFB43DC86B?lp_asin=B0DFLYY2H7&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J33" r:id="rId230" tooltip="https://www.amazon.it/dp/B0DFLYY2H7?psc=1"/>
+    <hyperlink ref="K33" r:id="rId231" tooltip="https://m.media-amazon.com/images/I/41n21y5gWdL._AC_US600_.jpg"/>
+    <hyperlink ref="L33" r:id="rId232" tooltip="https://www.amazon.it/dp/B0DFLYY2H7"/>
     <hyperlink ref="M33" r:id="rId233" tooltip="https://www.amazon.it/b?node=733005031"/>
     <hyperlink ref="N33" r:id="rId234"/>
-    <hyperlink ref="C34" r:id="rId235" tooltip="https://www.amazon.it/dp/B0DFLYY2H7"/>
-    <hyperlink ref="G34" r:id="rId236" tooltip="https://www.amazon.it/stores/VACMASTER/page/F372FF16-5498-423D-9923-A4EFB43DC86B?lp_asin=B0DFLYY2H7&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J34" r:id="rId237" tooltip="https://www.amazon.it/dp/B0DFLYY2H7?psc=1"/>
-    <hyperlink ref="K34" r:id="rId238" tooltip="https://m.media-amazon.com/images/I/41n21y5gWdL._AC_US600_.jpg"/>
-    <hyperlink ref="L34" r:id="rId239" tooltip="https://www.amazon.it/dp/B0DFLYY2H7"/>
-    <hyperlink ref="M34" r:id="rId240" tooltip="https://www.amazon.it/b?node=733005031"/>
-    <hyperlink ref="N34" r:id="rId241"/>
-    <hyperlink ref="AW34" r:id="rId242" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AUAKXO7WRPF4V"/>
-    <hyperlink ref="C35" r:id="rId243" tooltip="https://www.amazon.it/dp/B0FJFDG5PY"/>
-    <hyperlink ref="G35" r:id="rId244" tooltip="https://www.amazon.it/stores/Akitas/page/EE82F545-EF96-443C-8B75-30C504BE3C43?lp_asin=B0FJFDG5PY&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J35" r:id="rId245" tooltip="https://www.amazon.it/dp/B0FJFDG5PY?psc=1"/>
-    <hyperlink ref="K35" r:id="rId246" tooltip="https://m.media-amazon.com/images/I/41eJu8zeBKL._AC_US600_.jpg"/>
-    <hyperlink ref="L35" r:id="rId247" tooltip="https://www.amazon.it/dp/B0FJFDG5PY"/>
-    <hyperlink ref="M35" r:id="rId248" tooltip="https://www.amazon.it/b?node=733005031"/>
-    <hyperlink ref="N35" r:id="rId249"/>
-    <hyperlink ref="AW35" r:id="rId250" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3ZOAHYWM588P"/>
-    <hyperlink ref="C36" r:id="rId251" tooltip="https://www.amazon.it/dp/B0DT7CPRW2"/>
-    <hyperlink ref="G36" r:id="rId252" tooltip="https://www.amazon.it/stores/Shark/page/6BE84762-FC53-42E0-873B-1D7826105161?lp_asin=B0DT7CPRW2&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J36" r:id="rId253" tooltip="https://www.amazon.it/dp/B0DT7CPRW2?psc=1"/>
-    <hyperlink ref="K36" r:id="rId254" tooltip="https://m.media-amazon.com/images/I/415bHD1YKaL._AC_US600_.jpg"/>
-    <hyperlink ref="L36" r:id="rId255" tooltip="https://www.amazon.it/dp/B0DT7CPRW2"/>
-    <hyperlink ref="M36" r:id="rId256" tooltip="https://www.amazon.it/b?node=733005031"/>
-    <hyperlink ref="N36" r:id="rId257"/>
-    <hyperlink ref="AW36" r:id="rId258" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2XLKW1ZJ6I33S"/>
-    <hyperlink ref="C37" r:id="rId259" tooltip="https://www.amazon.it/dp/B0H97LW9DL"/>
-    <hyperlink ref="G37" r:id="rId260" tooltip="https://www.amazon.it/stores/Rispostaimmediatain24ore/page/DC11DA78-3928-4F1D-8E2F-8AD84D6FF0A2?lp_asin=B0H97LW9DL&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J37" r:id="rId261" tooltip="https://www.amazon.it/dp/B0H97LW9DL?psc=1"/>
-    <hyperlink ref="K37" r:id="rId262" tooltip="https://images-na.ssl-images-amazon.com/images/I/51LnggCx6eL._AC_US600_.jpg"/>
-    <hyperlink ref="L37" r:id="rId263" tooltip="https://www.amazon.it/dp/B0H97LW9DL"/>
-    <hyperlink ref="M37" r:id="rId264" tooltip="https://www.amazon.it/b?node=733005031"/>
-    <hyperlink ref="N37" r:id="rId265"/>
-    <hyperlink ref="AW37" r:id="rId266" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1SGZEKAW8X162"/>
-    <hyperlink ref="C38" r:id="rId267" tooltip="https://www.amazon.it/dp/B0H4TXR27S"/>
-    <hyperlink ref="G38" r:id="rId268" tooltip="https://www.amazon.it/stores/Redkey/page/D0F8E94D-480F-4BD7-ADC2-FEE4358EEB34?lp_asin=B0H4TXR27S&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J38" r:id="rId269" tooltip="https://www.amazon.it/dp/B0H4TXR27S?psc=1"/>
-    <hyperlink ref="K38" r:id="rId270" tooltip="https://m.media-amazon.com/images/I/41f8wwTeaGL._AC_US600_.jpg"/>
-    <hyperlink ref="L38" r:id="rId271" tooltip="https://www.amazon.it/dp/B0H4TXR27S"/>
+    <hyperlink ref="AW33" r:id="rId235" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AUAKXO7WRPF4V"/>
+    <hyperlink ref="C34" r:id="rId236" tooltip="https://www.amazon.it/dp/B0FJFDG5PY"/>
+    <hyperlink ref="G34" r:id="rId237" tooltip="https://www.amazon.it/stores/Akitas/page/EE82F545-EF96-443C-8B75-30C504BE3C43?lp_asin=B0FJFDG5PY&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J34" r:id="rId238" tooltip="https://www.amazon.it/dp/B0FJFDG5PY?psc=1"/>
+    <hyperlink ref="K34" r:id="rId239" tooltip="https://m.media-amazon.com/images/I/41eJu8zeBKL._AC_US600_.jpg"/>
+    <hyperlink ref="L34" r:id="rId240" tooltip="https://www.amazon.it/dp/B0FJFDG5PY"/>
+    <hyperlink ref="M34" r:id="rId241" tooltip="https://www.amazon.it/b?node=733005031"/>
+    <hyperlink ref="N34" r:id="rId242"/>
+    <hyperlink ref="AW34" r:id="rId243" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3ZOAHYWM588P"/>
+    <hyperlink ref="C35" r:id="rId244" tooltip="https://www.amazon.it/dp/B0DT7CPRW2"/>
+    <hyperlink ref="G35" r:id="rId245" tooltip="https://www.amazon.it/stores/Shark/page/6BE84762-FC53-42E0-873B-1D7826105161?lp_asin=B0DT7CPRW2&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J35" r:id="rId246" tooltip="https://www.amazon.it/dp/B0DT7CPRW2?psc=1"/>
+    <hyperlink ref="K35" r:id="rId247" tooltip="https://m.media-amazon.com/images/I/415bHD1YKaL._AC_US600_.jpg"/>
+    <hyperlink ref="L35" r:id="rId248" tooltip="https://www.amazon.it/dp/B0DT7CPRW2"/>
+    <hyperlink ref="M35" r:id="rId249" tooltip="https://www.amazon.it/b?node=733005031"/>
+    <hyperlink ref="N35" r:id="rId250"/>
+    <hyperlink ref="AW35" r:id="rId251" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2XLKW1ZJ6I33S"/>
+    <hyperlink ref="C36" r:id="rId252" tooltip="https://www.amazon.it/dp/B0H97LW9DL"/>
+    <hyperlink ref="G36" r:id="rId253" tooltip="https://www.amazon.it/stores/Rispostaimmediatain24ore/page/DC11DA78-3928-4F1D-8E2F-8AD84D6FF0A2?lp_asin=B0H97LW9DL&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J36" r:id="rId254" tooltip="https://www.amazon.it/dp/B0H97LW9DL?psc=1"/>
+    <hyperlink ref="K36" r:id="rId255" tooltip="https://images-na.ssl-images-amazon.com/images/I/51LnggCx6eL._AC_US600_.jpg"/>
+    <hyperlink ref="L36" r:id="rId256" tooltip="https://www.amazon.it/dp/B0H97LW9DL"/>
+    <hyperlink ref="M36" r:id="rId257" tooltip="https://www.amazon.it/b?node=733005031"/>
+    <hyperlink ref="N36" r:id="rId258"/>
+    <hyperlink ref="AW36" r:id="rId259" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1SGZEKAW8X162"/>
+    <hyperlink ref="C37" r:id="rId260" tooltip="https://www.amazon.it/dp/B0H4TXR27S"/>
+    <hyperlink ref="G37" r:id="rId261" tooltip="https://www.amazon.it/stores/Redkey/page/D0F8E94D-480F-4BD7-ADC2-FEE4358EEB34?lp_asin=B0H4TXR27S&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J37" r:id="rId262" tooltip="https://www.amazon.it/dp/B0H4TXR27S?psc=1"/>
+    <hyperlink ref="K37" r:id="rId263" tooltip="https://m.media-amazon.com/images/I/41f8wwTeaGL._AC_US600_.jpg"/>
+    <hyperlink ref="L37" r:id="rId264" tooltip="https://www.amazon.it/dp/B0H4TXR27S"/>
+    <hyperlink ref="M37" r:id="rId265" tooltip="https://www.amazon.it/b?node=733005031"/>
+    <hyperlink ref="N37" r:id="rId266"/>
+    <hyperlink ref="C38" r:id="rId267" tooltip="https://www.amazon.it/dp/B0GXVNJC4S"/>
+    <hyperlink ref="G38" r:id="rId268" tooltip="https://www.amazon.it/Cecotec/b/ref=bl_dp_s_web_19986335031?ie=UTF8&amp;node=19986335031&amp;field-lbr_brands_browse-bin=Cecotec"/>
+    <hyperlink ref="J38" r:id="rId269" tooltip="https://www.amazon.it/dp/B0GXVNJC4S?psc=1"/>
+    <hyperlink ref="K38" r:id="rId270" tooltip="https://images-na.ssl-images-amazon.com/images/I/81yDnM5PJYL._AC_US600_.jpg"/>
+    <hyperlink ref="L38" r:id="rId271" tooltip="https://www.amazon.it/dp/B0GXVNJC4S"/>
     <hyperlink ref="M38" r:id="rId272" tooltip="https://www.amazon.it/b?node=733005031"/>
     <hyperlink ref="N38" r:id="rId273"/>
-    <hyperlink ref="C39" r:id="rId274" tooltip="https://www.amazon.it/dp/B0GXVNJC4S"/>
-    <hyperlink ref="G39" r:id="rId275" tooltip="https://www.amazon.it/Cecotec/b/ref=bl_dp_s_web_19986335031?ie=UTF8&amp;node=19986335031&amp;field-lbr_brands_browse-bin=Cecotec"/>
-    <hyperlink ref="J39" r:id="rId276" tooltip="https://www.amazon.it/dp/B0GXVNJC4S?psc=1"/>
-    <hyperlink ref="K39" r:id="rId277" tooltip="https://images-na.ssl-images-amazon.com/images/I/81yDnM5PJYL._AC_US600_.jpg"/>
-    <hyperlink ref="L39" r:id="rId278" tooltip="https://www.amazon.it/dp/B0GXVNJC4S"/>
+    <hyperlink ref="C39" r:id="rId274" tooltip="https://www.amazon.it/dp/B0HBWJY7M3"/>
+    <hyperlink ref="G39" r:id="rId275" tooltip="https://www.amazon.it/stores/VACMASTER/page/F372FF16-5498-423D-9923-A4EFB43DC86B?lp_asin=B0HBWJY7M3&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J39" r:id="rId276" tooltip="https://www.amazon.it/dp/B0HBWJY7M3?psc=1"/>
+    <hyperlink ref="K39" r:id="rId277" tooltip="https://m.media-amazon.com/images/I/414oCMjoraL._AC_US600_.jpg"/>
+    <hyperlink ref="L39" r:id="rId278" tooltip="https://www.amazon.it/dp/B0HBWJY7M3"/>
     <hyperlink ref="M39" r:id="rId279" tooltip="https://www.amazon.it/b?node=733005031"/>
     <hyperlink ref="N39" r:id="rId280"/>
-    <hyperlink ref="C40" r:id="rId281" tooltip="https://www.amazon.it/dp/B0HBWJY7M3"/>
-    <hyperlink ref="G40" r:id="rId282" tooltip="https://www.amazon.it/stores/VACMASTER/page/F372FF16-5498-423D-9923-A4EFB43DC86B?lp_asin=B0HBWJY7M3&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J40" r:id="rId283" tooltip="https://www.amazon.it/dp/B0HBWJY7M3?psc=1"/>
-    <hyperlink ref="K40" r:id="rId284" tooltip="https://m.media-amazon.com/images/I/414oCMjoraL._AC_US600_.jpg"/>
-    <hyperlink ref="L40" r:id="rId285" tooltip="https://www.amazon.it/dp/B0HBWJY7M3"/>
+    <hyperlink ref="C40" r:id="rId281" tooltip="https://www.amazon.it/dp/B0DJD5C46J"/>
+    <hyperlink ref="G40" r:id="rId282" tooltip="https://www.amazon.it/Cecotec/b/ref=bl_dp_s_web_19986335031?ie=UTF8&amp;node=19986335031&amp;field-lbr_brands_browse-bin=Cecotec"/>
+    <hyperlink ref="J40" r:id="rId283" tooltip="https://www.amazon.it/dp/B0DJD5C46J?psc=1"/>
+    <hyperlink ref="K40" r:id="rId284" tooltip="https://images-na.ssl-images-amazon.com/images/I/715qquaM5jL._AC_US600_.jpg"/>
+    <hyperlink ref="L40" r:id="rId285" tooltip="https://www.amazon.it/dp/B0DJD5C46J"/>
     <hyperlink ref="M40" r:id="rId286" tooltip="https://www.amazon.it/b?node=733005031"/>
     <hyperlink ref="N40" r:id="rId287"/>
-    <hyperlink ref="C41" r:id="rId288" tooltip="https://www.amazon.it/dp/B0DJD5C46J"/>
-    <hyperlink ref="G41" r:id="rId289" tooltip="https://www.amazon.it/Cecotec/b/ref=bl_dp_s_web_19986335031?ie=UTF8&amp;node=19986335031&amp;field-lbr_brands_browse-bin=Cecotec"/>
-    <hyperlink ref="J41" r:id="rId290" tooltip="https://www.amazon.it/dp/B0DJD5C46J?psc=1"/>
-    <hyperlink ref="K41" r:id="rId291" tooltip="https://images-na.ssl-images-amazon.com/images/I/715qquaM5jL._AC_US600_.jpg"/>
-    <hyperlink ref="L41" r:id="rId292" tooltip="https://www.amazon.it/dp/B0DJD5C46J"/>
-    <hyperlink ref="M41" r:id="rId293" tooltip="https://www.amazon.it/b?node=733005031"/>
-    <hyperlink ref="N41" r:id="rId294"/>
-    <hyperlink ref="AW41" r:id="rId295" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1RXW3TLJ3ZGW0"/>
-    <hyperlink ref="C42" r:id="rId296" tooltip="https://www.amazon.it/dp/B0GDCZ7BWK"/>
-    <hyperlink ref="G42" r:id="rId297" tooltip="https://www.amazon.it/stores/HYCHIKABETTERTOOLSFORBETTERLIFE/page/15D103CB-D5AC-4757-BA0D-C568361A5A34?lp_asin=B0GDCZ7BWK&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J42" r:id="rId298" tooltip="https://www.amazon.it/dp/B0GDCZ7BWK?psc=1"/>
-    <hyperlink ref="K42" r:id="rId299" tooltip="https://m.media-amazon.com/images/I/51aWYbD9oWL._AC_US600_.jpg"/>
-    <hyperlink ref="L42" r:id="rId300" tooltip="https://www.amazon.it/dp/B0GDCZ7BWK"/>
+    <hyperlink ref="AW40" r:id="rId288" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1RXW3TLJ3ZGW0"/>
+    <hyperlink ref="C41" r:id="rId289" tooltip="https://www.amazon.it/dp/B0GDCZ7BWK"/>
+    <hyperlink ref="G41" r:id="rId290" tooltip="https://www.amazon.it/stores/HYCHIKABETTERTOOLSFORBETTERLIFE/page/15D103CB-D5AC-4757-BA0D-C568361A5A34?lp_asin=B0GDCZ7BWK&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J41" r:id="rId291" tooltip="https://www.amazon.it/dp/B0GDCZ7BWK?psc=1"/>
+    <hyperlink ref="K41" r:id="rId292" tooltip="https://m.media-amazon.com/images/I/51aWYbD9oWL._AC_US600_.jpg"/>
+    <hyperlink ref="L41" r:id="rId293" tooltip="https://www.amazon.it/dp/B0GDCZ7BWK"/>
+    <hyperlink ref="M41" r:id="rId294" tooltip="https://www.amazon.it/b?node=733005031"/>
+    <hyperlink ref="N41" r:id="rId295"/>
+    <hyperlink ref="C42" r:id="rId296" tooltip="https://www.amazon.it/dp/B0BPZJSXCQ"/>
+    <hyperlink ref="G42" r:id="rId297" tooltip="https://www.amazon.it/Cecotec/b/ref=bl_dp_s_web_19986335031?ie=UTF8&amp;node=19986335031&amp;field-lbr_brands_browse-bin=Cecotec"/>
+    <hyperlink ref="J42" r:id="rId298" tooltip="https://www.amazon.it/dp/B0BPZJSXCQ?psc=1"/>
+    <hyperlink ref="K42" r:id="rId299" tooltip="https://m.media-amazon.com/images/I/41-V4acAJLL._AC_US600_.jpg"/>
+    <hyperlink ref="L42" r:id="rId300" tooltip="https://www.amazon.it/dp/B0BPZJSXCQ"/>
     <hyperlink ref="M42" r:id="rId301" tooltip="https://www.amazon.it/b?node=733005031"/>
     <hyperlink ref="N42" r:id="rId302"/>
-    <hyperlink ref="C43" r:id="rId303" tooltip="https://www.amazon.it/dp/B0BPZJSXCQ"/>
-    <hyperlink ref="G43" r:id="rId304" tooltip="https://www.amazon.it/Cecotec/b/ref=bl_dp_s_web_19986335031?ie=UTF8&amp;node=19986335031&amp;field-lbr_brands_browse-bin=Cecotec"/>
-    <hyperlink ref="J43" r:id="rId305" tooltip="https://www.amazon.it/dp/B0BPZJSXCQ?psc=1"/>
-    <hyperlink ref="K43" r:id="rId306" tooltip="https://m.media-amazon.com/images/I/41-V4acAJLL._AC_US600_.jpg"/>
-    <hyperlink ref="L43" r:id="rId307" tooltip="https://www.amazon.it/dp/B0BPZJSXCQ"/>
-    <hyperlink ref="M43" r:id="rId308" tooltip="https://www.amazon.it/b?node=733005031"/>
-    <hyperlink ref="N43" r:id="rId309"/>
-    <hyperlink ref="AW43" r:id="rId310" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1PTIZUJDIGRO9"/>
-    <hyperlink ref="C44" r:id="rId311" tooltip="https://www.amazon.it/dp/B0GFF7C519"/>
-    <hyperlink ref="G44" r:id="rId312" tooltip="https://www.amazon.it/stores/Akitas/page/EE82F545-EF96-443C-8B75-30C504BE3C43?lp_asin=B0GFF7C519&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J44" r:id="rId313" tooltip="https://www.amazon.it/dp/B0GFF7C519?psc=1"/>
-    <hyperlink ref="K44" r:id="rId314" tooltip="https://m.media-amazon.com/images/I/41qPnZFK2xL._AC_US600_.jpg"/>
-    <hyperlink ref="L44" r:id="rId315" tooltip="https://www.amazon.it/dp/B0GFF7C519"/>
-    <hyperlink ref="M44" r:id="rId316" tooltip="https://www.amazon.it/b?node=733005031"/>
-    <hyperlink ref="N44" r:id="rId317"/>
-    <hyperlink ref="AW44" r:id="rId318" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3ZOAHYWM588P"/>
-    <hyperlink ref="C45" r:id="rId319" tooltip="https://www.amazon.it/dp/B0H3KVMBCH"/>
-    <hyperlink ref="G45" r:id="rId320" tooltip="https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=MELLWIN"/>
-    <hyperlink ref="J45" r:id="rId321" tooltip="https://www.amazon.it/dp/B0H3KVMBCH?psc=1"/>
-    <hyperlink ref="K45" r:id="rId322" tooltip="https://m.media-amazon.com/images/I/41W3WF+EhbL._AC_US600_.jpg"/>
-    <hyperlink ref="L45" r:id="rId323" tooltip="https://www.amazon.it/dp/B0H3KVMBCH"/>
-    <hyperlink ref="M45" r:id="rId324" tooltip="https://www.amazon.it/b?node=733005031"/>
-    <hyperlink ref="N45" r:id="rId325"/>
-    <hyperlink ref="AW45" r:id="rId326" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=ABSTVEQNNON26"/>
-    <hyperlink ref="C46" r:id="rId327" tooltip="https://www.amazon.it/dp/B0FXX52XPP"/>
-    <hyperlink ref="G46" r:id="rId328" tooltip="https://www.amazon.it/stores/POLTI/page/79293619-D61E-4C36-99D5-4729A55252D6?lp_asin=B0FXX52XPP&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J46" r:id="rId329" tooltip="https://www.amazon.it/dp/B0FXX52XPP?psc=1"/>
-    <hyperlink ref="K46" r:id="rId330" tooltip="https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T2/images/I/31Smsdr+waL._AC_US600_.jpg"/>
-    <hyperlink ref="L46" r:id="rId331" tooltip="https://www.amazon.it/dp/B0FXX52XPP"/>
+    <hyperlink ref="AW42" r:id="rId303" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1PTIZUJDIGRO9"/>
+    <hyperlink ref="C43" r:id="rId304" tooltip="https://www.amazon.it/dp/B0GFF7C519"/>
+    <hyperlink ref="G43" r:id="rId305" tooltip="https://www.amazon.it/stores/Akitas/page/EE82F545-EF96-443C-8B75-30C504BE3C43?lp_asin=B0GFF7C519&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J43" r:id="rId306" tooltip="https://www.amazon.it/dp/B0GFF7C519?psc=1"/>
+    <hyperlink ref="K43" r:id="rId307" tooltip="https://m.media-amazon.com/images/I/41qPnZFK2xL._AC_US600_.jpg"/>
+    <hyperlink ref="L43" r:id="rId308" tooltip="https://www.amazon.it/dp/B0GFF7C519"/>
+    <hyperlink ref="M43" r:id="rId309" tooltip="https://www.amazon.it/b?node=733005031"/>
+    <hyperlink ref="N43" r:id="rId310"/>
+    <hyperlink ref="AW43" r:id="rId311" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3ZOAHYWM588P"/>
+    <hyperlink ref="C44" r:id="rId312" tooltip="https://www.amazon.it/dp/B0H3KVMBCH"/>
+    <hyperlink ref="G44" r:id="rId313" tooltip="https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=MELLWIN"/>
+    <hyperlink ref="J44" r:id="rId314" tooltip="https://www.amazon.it/dp/B0H3KVMBCH?psc=1"/>
+    <hyperlink ref="K44" r:id="rId315" tooltip="https://m.media-amazon.com/images/I/41W3WF+EhbL._AC_US600_.jpg"/>
+    <hyperlink ref="L44" r:id="rId316" tooltip="https://www.amazon.it/dp/B0H3KVMBCH"/>
+    <hyperlink ref="M44" r:id="rId317" tooltip="https://www.amazon.it/b?node=733005031"/>
+    <hyperlink ref="N44" r:id="rId318"/>
+    <hyperlink ref="AW44" r:id="rId319" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=ABSTVEQNNON26"/>
+    <hyperlink ref="C45" r:id="rId320" tooltip="https://www.amazon.it/dp/B0FXX52XPP"/>
+    <hyperlink ref="G45" r:id="rId321" tooltip="https://www.amazon.it/stores/POLTI/page/79293619-D61E-4C36-99D5-4729A55252D6?lp_asin=B0FXX52XPP&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J45" r:id="rId322" tooltip="https://www.amazon.it/dp/B0FXX52XPP?psc=1"/>
+    <hyperlink ref="K45" r:id="rId323" tooltip="https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T2/images/I/31Smsdr+waL._AC_US600_.jpg"/>
+    <hyperlink ref="L45" r:id="rId324" tooltip="https://www.amazon.it/dp/B0FXX52XPP"/>
+    <hyperlink ref="M45" r:id="rId325" tooltip="https://www.amazon.it/b?node=733005031"/>
+    <hyperlink ref="N45" r:id="rId326"/>
+    <hyperlink ref="C46" r:id="rId327" tooltip="https://www.amazon.it/dp/B0H7C5V7MZ"/>
+    <hyperlink ref="G46" r:id="rId328" tooltip="https://www.amazon.it/stores/aspirapolvereabatteria/page/F0D8BDB2-BD7B-4C1C-9C40-2225E4C1C262?lp_asin=B0H7C5V7MZ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J46" r:id="rId329" tooltip="https://www.amazon.it/dp/B0H7C5V7MZ?psc=1"/>
+    <hyperlink ref="K46" r:id="rId330" tooltip="https://m.media-amazon.com/images/I/41cQk55jQqL._AC_US600_.jpg"/>
+    <hyperlink ref="L46" r:id="rId331" tooltip="https://www.amazon.it/dp/B0H7C5V7MZ"/>
     <hyperlink ref="M46" r:id="rId332" tooltip="https://www.amazon.it/b?node=733005031"/>
     <hyperlink ref="N46" r:id="rId333"/>
-    <hyperlink ref="C47" r:id="rId334" tooltip="https://www.amazon.it/dp/B0H7C5V7MZ"/>
-    <hyperlink ref="G47" r:id="rId335" tooltip="https://www.amazon.it/stores/aspirapolvereabatteria/page/F0D8BDB2-BD7B-4C1C-9C40-2225E4C1C262?lp_asin=B0H7C5V7MZ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J47" r:id="rId336" tooltip="https://www.amazon.it/dp/B0H7C5V7MZ?psc=1"/>
-    <hyperlink ref="K47" r:id="rId337" tooltip="https://m.media-amazon.com/images/I/41cQk55jQqL._AC_US600_.jpg"/>
-    <hyperlink ref="L47" r:id="rId338" tooltip="https://www.amazon.it/dp/B0H7C5V7MZ"/>
-    <hyperlink ref="M47" r:id="rId339" tooltip="https://www.amazon.it/b?node=733005031"/>
-    <hyperlink ref="N47" r:id="rId340"/>
-    <hyperlink ref="AW47" r:id="rId341" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A97DWD1P7ED3E"/>
-    <hyperlink ref="C48" r:id="rId342" tooltip="https://www.amazon.it/dp/B0F9PLL56G"/>
-    <hyperlink ref="G48" r:id="rId343" tooltip="https://www.amazon.it/Vax/b/ref=bl_dp_s_web_16065939031?ie=UTF8&amp;node=16065939031&amp;field-lbr_brands_browse-bin=Vax"/>
-    <hyperlink ref="J48" r:id="rId344" tooltip="https://www.amazon.it/dp/B0F9PLL56G?psc=1"/>
-    <hyperlink ref="K48" r:id="rId345" tooltip="https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T4/images/I/419W+KsIGaL._AC_US600_.jpg"/>
-    <hyperlink ref="L48" r:id="rId346" tooltip="https://www.amazon.it/dp/B0F9PLL56G"/>
+    <hyperlink ref="AW46" r:id="rId334" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A97DWD1P7ED3E"/>
+    <hyperlink ref="C47" r:id="rId335" tooltip="https://www.amazon.it/dp/B0F9PLL56G"/>
+    <hyperlink ref="G47" r:id="rId336" tooltip="https://www.amazon.it/Vax/b/ref=bl_dp_s_web_16065939031?ie=UTF8&amp;node=16065939031&amp;field-lbr_brands_browse-bin=Vax"/>
+    <hyperlink ref="J47" r:id="rId337" tooltip="https://www.amazon.it/dp/B0F9PLL56G?psc=1"/>
+    <hyperlink ref="K47" r:id="rId338" tooltip="https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T4/images/I/419W+KsIGaL._AC_US600_.jpg"/>
+    <hyperlink ref="L47" r:id="rId339" tooltip="https://www.amazon.it/dp/B0F9PLL56G"/>
+    <hyperlink ref="M47" r:id="rId340" tooltip="https://www.amazon.it/b?node=733005031"/>
+    <hyperlink ref="N47" r:id="rId341"/>
+    <hyperlink ref="C48" r:id="rId342" tooltip="https://www.amazon.it/dp/B0H263J8GJ"/>
+    <hyperlink ref="G48" r:id="rId343" tooltip="https://www.amazon.it/stores/Hearten/page/91157C36-9CCC-4DA6-833F-59782FACE3E0?lp_asin=B0H263J8GJ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J48" r:id="rId344" tooltip="https://www.amazon.it/dp/B0H263J8GJ?psc=1"/>
+    <hyperlink ref="K48" r:id="rId345" tooltip="https://m.media-amazon.com/images/I/4163ZUVBqYL._AC_US600_.jpg"/>
+    <hyperlink ref="L48" r:id="rId346" tooltip="https://www.amazon.it/dp/B0H263J8GJ"/>
     <hyperlink ref="M48" r:id="rId347" tooltip="https://www.amazon.it/b?node=733005031"/>
     <hyperlink ref="N48" r:id="rId348"/>
-    <hyperlink ref="C49" r:id="rId349" tooltip="https://www.amazon.it/dp/B0H263J8GJ"/>
-    <hyperlink ref="G49" r:id="rId350" tooltip="https://www.amazon.it/stores/Hearten/page/91157C36-9CCC-4DA6-833F-59782FACE3E0?lp_asin=B0H263J8GJ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J49" r:id="rId351" tooltip="https://www.amazon.it/dp/B0H263J8GJ?psc=1"/>
-    <hyperlink ref="K49" r:id="rId352" tooltip="https://m.media-amazon.com/images/I/4163ZUVBqYL._AC_US600_.jpg"/>
-    <hyperlink ref="L49" r:id="rId353" tooltip="https://www.amazon.it/dp/B0H263J8GJ"/>
-    <hyperlink ref="M49" r:id="rId354" tooltip="https://www.amazon.it/b?node=733005031"/>
-    <hyperlink ref="N49" r:id="rId355"/>
-    <hyperlink ref="AW49" r:id="rId356" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AGFI912YUQRG6"/>
-    <hyperlink ref="C50" r:id="rId357" tooltip="https://www.amazon.it/dp/B086Q46MMD"/>
-    <hyperlink ref="G50" r:id="rId358" tooltip="https://www.amazon.it/stores/STANHOME/page/CF140807-E9D9-4EE4-98E8-28F83571D17F?lp_asin=B086Q46MMD&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J50" r:id="rId359" tooltip="https://www.amazon.it/dp/B086Q46MMD?psc=1"/>
-    <hyperlink ref="K50" r:id="rId360" tooltip="https://m.media-amazon.com/images/I/31hUTFxCzpL._AC_US600_.jpg"/>
-    <hyperlink ref="L50" r:id="rId361" tooltip="https://www.amazon.it/dp/B086Q46MMD"/>
-    <hyperlink ref="M50" r:id="rId362" tooltip="https://www.amazon.it/b?node=733005031"/>
-    <hyperlink ref="N50" r:id="rId363"/>
-    <hyperlink ref="AW50" r:id="rId364" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1FKDALFGWQLQF"/>
-    <hyperlink ref="C51" r:id="rId365" tooltip="https://www.amazon.it/dp/B0DX2J6DW2"/>
-    <hyperlink ref="G51" r:id="rId366" tooltip="https://www.amazon.it/stores/Akitas/page/EE82F545-EF96-443C-8B75-30C504BE3C43?lp_asin=B0DX2J6DW2&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J51" r:id="rId367" tooltip="https://www.amazon.it/dp/B0DX2J6DW2?psc=1"/>
-    <hyperlink ref="K51" r:id="rId368" tooltip="https://m.media-amazon.com/images/I/41DlwHQxtaL._AC_US600_.jpg"/>
-    <hyperlink ref="L51" r:id="rId369" tooltip="https://www.amazon.it/dp/B0DX2J6DW2"/>
-    <hyperlink ref="M51" r:id="rId370" tooltip="https://www.amazon.it/b?node=733005031"/>
-    <hyperlink ref="N51" r:id="rId371"/>
-    <hyperlink ref="AW51" r:id="rId372" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3ZOAHYWM588P"/>
+    <hyperlink ref="AW48" r:id="rId349" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AGFI912YUQRG6"/>
+    <hyperlink ref="C49" r:id="rId350" tooltip="https://www.amazon.it/dp/B0DX2J6DW2"/>
+    <hyperlink ref="G49" r:id="rId351" tooltip="https://www.amazon.it/stores/Akitas/page/EE82F545-EF96-443C-8B75-30C504BE3C43?lp_asin=B0DX2J6DW2&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J49" r:id="rId352" tooltip="https://www.amazon.it/dp/B0DX2J6DW2?psc=1"/>
+    <hyperlink ref="K49" r:id="rId353" tooltip="https://m.media-amazon.com/images/I/41DlwHQxtaL._AC_US600_.jpg"/>
+    <hyperlink ref="L49" r:id="rId354" tooltip="https://www.amazon.it/dp/B0DX2J6DW2"/>
+    <hyperlink ref="M49" r:id="rId355" tooltip="https://www.amazon.it/b?node=733005031"/>
+    <hyperlink ref="N49" r:id="rId356"/>
+    <hyperlink ref="AW49" r:id="rId357" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3ZOAHYWM588P"/>
   </hyperlinks>
-  <drawing r:id="rId373"/>
+  <drawing r:id="rId358"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" style="1" customWidth="1"/>
@@ -19389,18 +18828,18 @@
         </is>
       </c>
       <c r="B2" s="15">
-        <v>5452</v>
+        <v>4572</v>
       </c>
       <c r="C2" s="15">
-        <v>680641</v>
+        <v>667450</v>
       </c>
       <c r="D2" s="15"/>
       <c r="E2" s="15"/>
       <c r="F2" s="20">
-        <v>124.84244314013206</v>
+        <v>145.98643919510062</v>
       </c>
       <c r="G2" s="22">
-        <v>0.36324871743620496</v>
+        <v>0.326454837558015</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19421,7 +18860,7 @@
         <v>138.67236662106703</v>
       </c>
       <c r="G3" s="22">
-        <v>0.0974082217336265</v>
+        <v>0.1043912888254195</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19442,7 +18881,7 @@
         <v>91.12866242038217</v>
       </c>
       <c r="G4" s="22">
-        <v>0.10460390432407222</v>
+        <v>0.11210282042127812</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19463,7 +18902,7 @@
         <v>69.98964968152866</v>
       </c>
       <c r="G5" s="22">
-        <v>0.08368312345925778</v>
+        <v>0.0896822563370225</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19484,7 +18923,7 @@
         <v>64.97034596375617</v>
       </c>
       <c r="G6" s="22">
-        <v>0.08088480245186222</v>
+        <v>0.08668332738307748</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19505,7 +18944,7 @@
         <v>211.36421725239617</v>
       </c>
       <c r="G7" s="22">
-        <v>0.02085415417416217</v>
+        <v>0.022349161013923598</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19526,7 +18965,7 @@
         <v>130.17084282460138</v>
       </c>
       <c r="G8" s="22">
-        <v>0.02924911719634886</v>
+        <v>0.03134594787575866</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19547,7 +18986,7 @@
         <v>96.78873239436619</v>
       </c>
       <c r="G9" s="22">
-        <v>0.03784396029049237</v>
+        <v>0.04055694394858979</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19568,7 +19007,7 @@
         <v>139.33957219251337</v>
       </c>
       <c r="G10" s="22">
-        <v>0.024918382303950964</v>
+        <v>0.02670474830417708</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19589,7 +19028,7 @@
         <v>152.37867647058823</v>
       </c>
       <c r="G11" s="22">
-        <v>0.018122459857418883</v>
+        <v>0.019421635130310602</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19610,7 +19049,7 @@
         <v>199.98823529411766</v>
       </c>
       <c r="G12" s="22">
-        <v>0.011326537410886801</v>
+        <v>0.012138521956444126</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19631,7 +19070,7 @@
         <v>124.7448559670782</v>
       </c>
       <c r="G13" s="22">
-        <v>0.016190285828502897</v>
+        <v>0.0173509460906819</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19652,7 +19091,7 @@
         <v>99.98928571428571</v>
       </c>
       <c r="G14" s="22">
-        <v>0.018655473382637084</v>
+        <v>0.019992859692966797</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19673,7 +19112,7 @@
         <v>69.0</v>
       </c>
       <c r="G15" s="22">
-        <v>0.026584049570257846</v>
+        <v>0.028489825062477686</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19694,7 +19133,7 @@
         <v>58.675471698113206</v>
       </c>
       <c r="G16" s="22">
-        <v>0.017656073022852953</v>
+        <v>0.018921813637986434</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19715,7 +19154,7 @@
         <v>59.90047393364929</v>
       </c>
       <c r="G17" s="22">
-        <v>0.014058231727630089</v>
+        <v>0.015066047840057122</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19736,7 +19175,7 @@
         <v>114.75</v>
       </c>
       <c r="G18" s="22">
-        <v>0.007195682590445732</v>
+        <v>0.007711531595858622</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19757,7 +19196,7 @@
         <v>166.9787234042553</v>
       </c>
       <c r="G19" s="22">
-        <v>0.0031314544606569393</v>
+        <v>0.003355944305605141</v>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19778,7 +19217,7 @@
         <v>117.63636363636364</v>
       </c>
       <c r="G20" s="22">
-        <v>0.00439736158305017</v>
+        <v>0.004712602641913602</v>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19799,7 +19238,7 @@
         <v>119.49019607843137</v>
       </c>
       <c r="G21" s="22">
-        <v>0.0033979612232660403</v>
+        <v>0.0036415565869332383</v>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19820,7 +19259,7 @@
         <v>119.0</v>
       </c>
       <c r="G22" s="22">
-        <v>0.0025318142447864614</v>
+        <v>0.0027133166726169226</v>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19841,7 +19280,7 @@
         <v>249.0</v>
       </c>
       <c r="G23" s="22">
-        <v>0.0011992804317409553</v>
+        <v>0.001285255265976437</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19862,7 +19301,7 @@
         <v>140.0</v>
       </c>
       <c r="G24" s="22">
-        <v>0.0015990405756546072</v>
+        <v>0.0017136736879685827</v>
       </c>
     </row>
     <row r="25" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19883,7 +19322,7 @@
         <v>150.0</v>
       </c>
       <c r="G25" s="22">
-        <v>0.0012659071223932307</v>
+        <v>0.0013566583363084613</v>
       </c>
     </row>
     <row r="26" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19904,28 +19343,7 @@
         <v>90.0</v>
       </c>
       <c r="G26" s="22">
-        <v>0.0017322939569591577</v>
-      </c>
-    </row>
-    <row r="27" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="14" t="inlineStr">
-        <is>
-          <t>STANHOME</t>
-        </is>
-      </c>
-      <c r="B27" s="15">
-        <v>124</v>
-      </c>
-      <c r="C27" s="15">
-        <v>1860</v>
-      </c>
-      <c r="D27" s="15"/>
-      <c r="E27" s="15"/>
-      <c r="F27" s="20">
-        <v>15.0</v>
-      </c>
-      <c r="G27" s="22">
-        <v>0.008261709640882138</v>
+        <v>0.0018564798286326311</v>
       </c>
     </row>
   </sheetData>
@@ -19936,7 +19354,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" style="1" customWidth="1"/>
@@ -19989,18 +19407,18 @@
         </is>
       </c>
       <c r="B2" s="15">
-        <v>10164</v>
+        <v>9284</v>
       </c>
       <c r="C2" s="15">
-        <v>1259156</v>
+        <v>1245965</v>
       </c>
       <c r="D2" s="15"/>
       <c r="E2" s="15"/>
       <c r="F2" s="20">
-        <v>123.88390397481307</v>
+        <v>134.20562257647566</v>
       </c>
       <c r="G2" s="22">
-        <v>0.6771936837897262</v>
+        <v>0.6629061049625133</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20021,7 +19439,7 @@
         <v>69.98964968152866</v>
       </c>
       <c r="G3" s="22">
-        <v>0.08368312345925778</v>
+        <v>0.0896822563370225</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20042,7 +19460,7 @@
         <v>64.97034596375617</v>
       </c>
       <c r="G4" s="22">
-        <v>0.08088480245186222</v>
+        <v>0.08668332738307748</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20063,7 +19481,7 @@
         <v>139.33957219251337</v>
       </c>
       <c r="G5" s="22">
-        <v>0.024918382303950964</v>
+        <v>0.02670474830417708</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20084,7 +19502,7 @@
         <v>159.98809523809524</v>
       </c>
       <c r="G6" s="22">
-        <v>0.016789926044373377</v>
+        <v>0.01799357372367012</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20105,7 +19523,7 @@
         <v>99.98928571428571</v>
       </c>
       <c r="G7" s="22">
-        <v>0.018655473382637084</v>
+        <v>0.019992859692966797</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20126,7 +19544,7 @@
         <v>89.98979591836735</v>
       </c>
       <c r="G8" s="22">
-        <v>0.013058831367845958</v>
+        <v>0.013995001785076759</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20147,7 +19565,7 @@
         <v>89.98930481283422</v>
       </c>
       <c r="G9" s="22">
-        <v>0.012459191151975482</v>
+        <v>0.01335237415208854</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20168,7 +19586,7 @@
         <v>58.675471698113206</v>
       </c>
       <c r="G10" s="22">
-        <v>0.017656073022852953</v>
+        <v>0.018921813637986434</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20189,7 +19607,7 @@
         <v>129.0</v>
       </c>
       <c r="G11" s="22">
-        <v>0.007129055899793457</v>
+        <v>0.0076401285255265974</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20210,7 +19628,7 @@
         <v>59.90047393364929</v>
       </c>
       <c r="G12" s="22">
-        <v>0.014058231727630089</v>
+        <v>0.015066047840057122</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20231,7 +19649,7 @@
         <v>114.75</v>
       </c>
       <c r="G13" s="22">
-        <v>0.007195682590445732</v>
+        <v>0.007711531595858622</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20252,7 +19670,7 @@
         <v>117.63636363636364</v>
       </c>
       <c r="G14" s="22">
-        <v>0.00439736158305017</v>
+        <v>0.004712602641913602</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20273,7 +19691,7 @@
         <v>113.14814814814815</v>
       </c>
       <c r="G15" s="22">
-        <v>0.003597841295222866</v>
+        <v>0.003855765797929311</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20294,7 +19712,7 @@
         <v>86.36507936507937</v>
       </c>
       <c r="G16" s="22">
-        <v>0.004197481511093344</v>
+        <v>0.00449839343091753</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20315,7 +19733,7 @@
         <v>119.0</v>
       </c>
       <c r="G17" s="22">
-        <v>0.0025318142447864614</v>
+        <v>0.0027133166726169226</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20336,7 +19754,7 @@
         <v>140.0</v>
       </c>
       <c r="G18" s="22">
-        <v>0.0015990405756546072</v>
+        <v>0.0017136736879685827</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20357,28 +19775,7 @@
         <v>90.0</v>
       </c>
       <c r="G19" s="22">
-        <v>0.0017322939569591577</v>
-      </c>
-    </row>
-    <row r="20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="14" t="inlineStr">
-        <is>
-          <t>Stanhome S.p.A</t>
-        </is>
-      </c>
-      <c r="B20" s="15">
-        <v>124</v>
-      </c>
-      <c r="C20" s="15">
-        <v>1860</v>
-      </c>
-      <c r="D20" s="15"/>
-      <c r="E20" s="15"/>
-      <c r="F20" s="20">
-        <v>15.0</v>
-      </c>
-      <c r="G20" s="22">
-        <v>0.008261709640882138</v>
+        <v>0.0018564798286326311</v>
       </c>
     </row>
   </sheetData>
